--- a/Herpeton Anole Data.xlsx
+++ b/Herpeton Anole Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasminekesselring/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasminekesselring/Desktop/Anole_Biometry_Practice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1B7CEB6-7D63-D949-8C39-32E6CFE7A4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F72B804-6E6D-684B-B4FD-DD42D5646548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="840" windowWidth="28720" windowHeight="16980" xr2:uid="{5183197B-93B4-694E-BC06-28ADA81A1872}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{5183197B-93B4-694E-BC06-28ADA81A1872}"/>
   </bookViews>
   <sheets>
     <sheet name="Anole Master Sheet" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3172" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4305" uniqueCount="735">
   <si>
     <t>Collection_Date</t>
   </si>
@@ -1740,6 +1740,636 @@
   </si>
   <si>
     <t>Date_Dissected</t>
+  </si>
+  <si>
+    <t>CW001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trematode in oral cavity. 2 nematodes found in oral cavity as well. </t>
+  </si>
+  <si>
+    <t>CW002</t>
+  </si>
+  <si>
+    <t>17 nematodes in stomach</t>
+  </si>
+  <si>
+    <t>CW003</t>
+  </si>
+  <si>
+    <t>2 trematodes in mouth. 6 adult nematodes in stomach. Encysted nematodes present. Mystery egg-like parasites too??</t>
+  </si>
+  <si>
+    <t>CW004</t>
+  </si>
+  <si>
+    <t>CW005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 nematodes in stomach. No that is not a typo. </t>
+  </si>
+  <si>
+    <t>CW006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 trematode in oral cavity. </t>
+  </si>
+  <si>
+    <t>CW007</t>
+  </si>
+  <si>
+    <t>CW008</t>
+  </si>
+  <si>
+    <t>CW009</t>
+  </si>
+  <si>
+    <t>CW010</t>
+  </si>
+  <si>
+    <t>CW011</t>
+  </si>
+  <si>
+    <t>Encysted nematodes present</t>
+  </si>
+  <si>
+    <t>CW012</t>
+  </si>
+  <si>
+    <t>CW013</t>
+  </si>
+  <si>
+    <t>1 adult nematode in stomach; Encysted nematodes present</t>
+  </si>
+  <si>
+    <t>CW014</t>
+  </si>
+  <si>
+    <t>ants prey items</t>
+  </si>
+  <si>
+    <t>CW015</t>
+  </si>
+  <si>
+    <t>CW016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 trematodes in oral cavity/throat </t>
+  </si>
+  <si>
+    <t>CW017</t>
+  </si>
+  <si>
+    <t>CW018</t>
+  </si>
+  <si>
+    <t>Caterpillar prey item</t>
+  </si>
+  <si>
+    <t>CW019</t>
+  </si>
+  <si>
+    <t>CW020</t>
+  </si>
+  <si>
+    <t>Weird orange mouth lesion, photographed; 1 adult nematode in stomach</t>
+  </si>
+  <si>
+    <t>CW021</t>
+  </si>
+  <si>
+    <t>CW022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 adult nematodes. 1 in stomach, 1 encysted in body cavity musculature, and 1 attached to the surface of the colon. </t>
+  </si>
+  <si>
+    <t>CW023</t>
+  </si>
+  <si>
+    <t>1 adult nematode in stomach</t>
+  </si>
+  <si>
+    <t>CW024</t>
+  </si>
+  <si>
+    <t>1 adult nematode encysted on stomach</t>
+  </si>
+  <si>
+    <t>CW025</t>
+  </si>
+  <si>
+    <t>CW026</t>
+  </si>
+  <si>
+    <t>1 trematode in oral cavity. Beetle grub prey items, moth too</t>
+  </si>
+  <si>
+    <t>CW027</t>
+  </si>
+  <si>
+    <t>CW028</t>
+  </si>
+  <si>
+    <t>CW029</t>
+  </si>
+  <si>
+    <t>Mystery parasite. Definitely same thing as whatever was in the seminole county lizards.</t>
+  </si>
+  <si>
+    <t>CW030</t>
+  </si>
+  <si>
+    <t>CW031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 trematode in oral cavity. 1 nematode in stomach. Both saved. </t>
+  </si>
+  <si>
+    <t>CW032</t>
+  </si>
+  <si>
+    <t>CW033</t>
+  </si>
+  <si>
+    <t>CW034</t>
+  </si>
+  <si>
+    <t>CW035</t>
+  </si>
+  <si>
+    <t>CW036</t>
+  </si>
+  <si>
+    <t>CW037</t>
+  </si>
+  <si>
+    <t>CW038</t>
+  </si>
+  <si>
+    <t>CW039</t>
+  </si>
+  <si>
+    <t>CW041</t>
+  </si>
+  <si>
+    <t>7 adult nematodes in stomach</t>
+  </si>
+  <si>
+    <t>CW042</t>
+  </si>
+  <si>
+    <t>CW043</t>
+  </si>
+  <si>
+    <t>4 adult nematodes in stomach</t>
+  </si>
+  <si>
+    <t>CW044</t>
+  </si>
+  <si>
+    <t>CW045</t>
+  </si>
+  <si>
+    <t>CW046</t>
+  </si>
+  <si>
+    <t>CW047</t>
+  </si>
+  <si>
+    <t>CW048</t>
+  </si>
+  <si>
+    <t>CW049</t>
+  </si>
+  <si>
+    <t>CW050</t>
+  </si>
+  <si>
+    <t>CW051</t>
+  </si>
+  <si>
+    <t>CW052</t>
+  </si>
+  <si>
+    <t>CW053</t>
+  </si>
+  <si>
+    <t>CW054</t>
+  </si>
+  <si>
+    <t>CW055</t>
+  </si>
+  <si>
+    <t>CW056</t>
+  </si>
+  <si>
+    <t>8 nematodes in stomach</t>
+  </si>
+  <si>
+    <t>CW057</t>
+  </si>
+  <si>
+    <t>CW058</t>
+  </si>
+  <si>
+    <t>CW059</t>
+  </si>
+  <si>
+    <t>CW060</t>
+  </si>
+  <si>
+    <t>9 nematodes in stomach</t>
+  </si>
+  <si>
+    <t>CW061</t>
+  </si>
+  <si>
+    <t>CW062</t>
+  </si>
+  <si>
+    <t>18 nematodes in stomach</t>
+  </si>
+  <si>
+    <t>CW063</t>
+  </si>
+  <si>
+    <t>CW064</t>
+  </si>
+  <si>
+    <t>CW065</t>
+  </si>
+  <si>
+    <t>CW066</t>
+  </si>
+  <si>
+    <t>CW067</t>
+  </si>
+  <si>
+    <t>CW068</t>
+  </si>
+  <si>
+    <t>3 ro larvae encysted near heart.  Encysted nematodes present</t>
+  </si>
+  <si>
+    <t>CW069</t>
+  </si>
+  <si>
+    <t>CW070</t>
+  </si>
+  <si>
+    <t>Roach prey item. No photo</t>
+  </si>
+  <si>
+    <t>CW071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 ro larvae encysted behind stomach. 1 nematode in stomach. </t>
+  </si>
+  <si>
+    <t>CW072</t>
+  </si>
+  <si>
+    <t>CW073</t>
+  </si>
+  <si>
+    <t>CW074</t>
+  </si>
+  <si>
+    <t>Moth prey item</t>
+  </si>
+  <si>
+    <t>CW075</t>
+  </si>
+  <si>
+    <t>CW076</t>
+  </si>
+  <si>
+    <t>CW077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">literally not one organ was clean. All throughout the muscles and viscera. Took over an hour. Ugh. </t>
+  </si>
+  <si>
+    <t>CW078</t>
+  </si>
+  <si>
+    <t>CW079</t>
+  </si>
+  <si>
+    <t>CW080</t>
+  </si>
+  <si>
+    <t>CW081</t>
+  </si>
+  <si>
+    <t>CW082</t>
+  </si>
+  <si>
+    <t>CW083</t>
+  </si>
+  <si>
+    <t>forgot to note what organs were affected :(</t>
+  </si>
+  <si>
+    <t>CW084</t>
+  </si>
+  <si>
+    <t>CW085</t>
+  </si>
+  <si>
+    <t>CW086</t>
+  </si>
+  <si>
+    <t>CW087</t>
+  </si>
+  <si>
+    <t>CW088</t>
+  </si>
+  <si>
+    <t>CW089</t>
+  </si>
+  <si>
+    <t>CW090</t>
+  </si>
+  <si>
+    <t>CW091</t>
+  </si>
+  <si>
+    <t>FGCU001</t>
+  </si>
+  <si>
+    <t>FGCU002</t>
+  </si>
+  <si>
+    <t>FGCU003</t>
+  </si>
+  <si>
+    <t>FGCU004</t>
+  </si>
+  <si>
+    <t>F?</t>
+  </si>
+  <si>
+    <t>FGCU005</t>
+  </si>
+  <si>
+    <t>FGCU006</t>
+  </si>
+  <si>
+    <t>FGCU007</t>
+  </si>
+  <si>
+    <t>FGCU008</t>
+  </si>
+  <si>
+    <t>FGCU009</t>
+  </si>
+  <si>
+    <t>FGCU010</t>
+  </si>
+  <si>
+    <t>FGCU011</t>
+  </si>
+  <si>
+    <t>FGCU012</t>
+  </si>
+  <si>
+    <t>FGCU013</t>
+  </si>
+  <si>
+    <t>FGCU014</t>
+  </si>
+  <si>
+    <t>FGCU015</t>
+  </si>
+  <si>
+    <t>FGCU016</t>
+  </si>
+  <si>
+    <t>FGCU017</t>
+  </si>
+  <si>
+    <t>FGCU018</t>
+  </si>
+  <si>
+    <t>FGCU019</t>
+  </si>
+  <si>
+    <t>FGCU020</t>
+  </si>
+  <si>
+    <t>FGCU021</t>
+  </si>
+  <si>
+    <t>FGCU022</t>
+  </si>
+  <si>
+    <t>FGCU023</t>
+  </si>
+  <si>
+    <t>FGCU024</t>
+  </si>
+  <si>
+    <t>FGCU025</t>
+  </si>
+  <si>
+    <t>FGCU026</t>
+  </si>
+  <si>
+    <t>FGCU027</t>
+  </si>
+  <si>
+    <t>FGCU028</t>
+  </si>
+  <si>
+    <t>FGCU029</t>
+  </si>
+  <si>
+    <t>FGCU030</t>
+  </si>
+  <si>
+    <t>FGCU031</t>
+  </si>
+  <si>
+    <t>FGCU032</t>
+  </si>
+  <si>
+    <t>FGCU033</t>
+  </si>
+  <si>
+    <t>FGCU034</t>
+  </si>
+  <si>
+    <t>FGCU035</t>
+  </si>
+  <si>
+    <t>FGCU036</t>
+  </si>
+  <si>
+    <t>FGCU037</t>
+  </si>
+  <si>
+    <t>FGCU038</t>
+  </si>
+  <si>
+    <t>FGCU039</t>
+  </si>
+  <si>
+    <t>FGCU040</t>
+  </si>
+  <si>
+    <t>FGCU041</t>
+  </si>
+  <si>
+    <t>FGCU042</t>
+  </si>
+  <si>
+    <t>FGCU043</t>
+  </si>
+  <si>
+    <t>FGCU044</t>
+  </si>
+  <si>
+    <t>FGCU045</t>
+  </si>
+  <si>
+    <t>FGCU046</t>
+  </si>
+  <si>
+    <t>FGCU047</t>
+  </si>
+  <si>
+    <t>FGCU048</t>
+  </si>
+  <si>
+    <t>FGCU049</t>
+  </si>
+  <si>
+    <t>FGCU050</t>
+  </si>
+  <si>
+    <t>FGCU051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juvenille </t>
+  </si>
+  <si>
+    <t>FGCU052</t>
+  </si>
+  <si>
+    <t>FGCU053</t>
+  </si>
+  <si>
+    <t>FGCU054</t>
+  </si>
+  <si>
+    <t>FGCU055</t>
+  </si>
+  <si>
+    <t>FGCU056</t>
+  </si>
+  <si>
+    <t>FGCU057</t>
+  </si>
+  <si>
+    <t>FGCU058</t>
+  </si>
+  <si>
+    <t>FGCU059</t>
+  </si>
+  <si>
+    <t>FGCU060</t>
+  </si>
+  <si>
+    <t>FGCU061</t>
+  </si>
+  <si>
+    <t>FGCU062</t>
+  </si>
+  <si>
+    <t>FGCU063</t>
+  </si>
+  <si>
+    <t>FGCU064</t>
+  </si>
+  <si>
+    <t>FGCU065</t>
+  </si>
+  <si>
+    <t>FGCU066</t>
+  </si>
+  <si>
+    <t>FGCU067</t>
+  </si>
+  <si>
+    <t>FGCU068</t>
+  </si>
+  <si>
+    <t>FGCU069</t>
+  </si>
+  <si>
+    <t>FGCU070</t>
+  </si>
+  <si>
+    <t>FGCU071</t>
+  </si>
+  <si>
+    <t>FGCU072</t>
+  </si>
+  <si>
+    <t>FGCU073</t>
+  </si>
+  <si>
+    <t>FGCU074</t>
+  </si>
+  <si>
+    <t>FGCU075</t>
+  </si>
+  <si>
+    <t>FGCU076</t>
+  </si>
+  <si>
+    <t>FGCU077</t>
+  </si>
+  <si>
+    <t>FGCU078</t>
+  </si>
+  <si>
+    <t>FGCU079</t>
+  </si>
+  <si>
+    <t>FGCU080</t>
+  </si>
+  <si>
+    <t>FGCU081</t>
+  </si>
+  <si>
+    <t>FGCU082</t>
+  </si>
+  <si>
+    <t>FGCU083</t>
+  </si>
+  <si>
+    <t>FGCU084</t>
+  </si>
+  <si>
+    <t>FGCU085</t>
+  </si>
+  <si>
+    <t>FGCU086</t>
+  </si>
+  <si>
+    <t>FGCU087</t>
+  </si>
+  <si>
+    <t>FGCU088</t>
+  </si>
+  <si>
+    <t>FGCU089</t>
+  </si>
+  <si>
+    <t>FGCU090</t>
   </si>
 </sst>
 </file>
@@ -1786,7 +2416,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1847,6 +2477,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1875,7 +2511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1968,6 +2604,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2303,7 +2945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3903B938-DE2F-DB42-860C-BE543646DADC}">
-  <dimension ref="A1:N371"/>
+  <dimension ref="A1:N551"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="19" customWidth="1"/>
@@ -18291,6 +18933,6014 @@
       </c>
       <c r="N371" s="19"/>
     </row>
+    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A372" s="3">
+        <v>46144</v>
+      </c>
+      <c r="B372" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="C372" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D372" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="E372" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="F372" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G372" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H372" s="6">
+        <v>46311</v>
+      </c>
+      <c r="I372" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J372" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K372" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L372" s="5">
+        <v>0</v>
+      </c>
+      <c r="M372" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N372" s="39" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A373" s="3">
+        <v>46144</v>
+      </c>
+      <c r="B373" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="C373" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D373" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="E373" s="4">
+        <v>3.37</v>
+      </c>
+      <c r="F373" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G373" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H373" s="6">
+        <v>46311</v>
+      </c>
+      <c r="I373" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J373" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K373" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L373" s="5">
+        <v>0</v>
+      </c>
+      <c r="M373" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N373" s="7" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="374" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A374" s="3">
+        <v>46144</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="C374" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D374" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E374" s="4">
+        <v>1.84</v>
+      </c>
+      <c r="F374" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G374" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H374" s="6">
+        <v>46311</v>
+      </c>
+      <c r="I374" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J374" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K374" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L374" s="5">
+        <v>0</v>
+      </c>
+      <c r="M374" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N374" s="39" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="375" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A375" s="3">
+        <v>46144</v>
+      </c>
+      <c r="B375" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C375" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D375" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E375" s="4">
+        <v>2.1</v>
+      </c>
+      <c r="F375" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G375" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H375" s="6">
+        <v>46311</v>
+      </c>
+      <c r="I375" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J375" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K375" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L375" s="5">
+        <v>0</v>
+      </c>
+      <c r="M375" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N375" s="4"/>
+    </row>
+    <row r="376" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A376" s="3">
+        <v>46144</v>
+      </c>
+      <c r="B376" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C376" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D376" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="E376" s="4">
+        <v>4.05</v>
+      </c>
+      <c r="F376" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G376" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H376" s="6">
+        <v>46311</v>
+      </c>
+      <c r="I376" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J376" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K376" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L376" s="5">
+        <v>0</v>
+      </c>
+      <c r="M376" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N376" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="377" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A377" s="3">
+        <v>46144</v>
+      </c>
+      <c r="B377" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="C377" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D377" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="E377" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="F377" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G377" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H377" s="6">
+        <v>46311</v>
+      </c>
+      <c r="I377" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J377" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K377" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L377" s="5">
+        <v>0</v>
+      </c>
+      <c r="M377" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N377" s="39" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="378" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A378" s="22">
+        <v>46144</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="C378" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D378" s="4">
+        <v>4</v>
+      </c>
+      <c r="E378" s="4">
+        <v>1.64</v>
+      </c>
+      <c r="F378" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G378" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H378" s="6">
+        <v>46311</v>
+      </c>
+      <c r="I378" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J378" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K378" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L378" s="5">
+        <v>0</v>
+      </c>
+      <c r="M378" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N378" s="4"/>
+    </row>
+    <row r="379" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A379" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="C379" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D379" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E379" s="4">
+        <v>4.88</v>
+      </c>
+      <c r="F379" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G379" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H379" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I379" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J379" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K379" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L379" s="5">
+        <v>0</v>
+      </c>
+      <c r="M379" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N379" s="4"/>
+    </row>
+    <row r="380" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A380" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="C380" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D380" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="E380" s="4">
+        <v>3.99</v>
+      </c>
+      <c r="F380" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G380" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H380" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I380" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J380" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K380" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L380" s="5">
+        <v>0</v>
+      </c>
+      <c r="M380" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N380" s="4"/>
+    </row>
+    <row r="381" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A381" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B381" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="C381" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D381" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="E381" s="4">
+        <v>2.14</v>
+      </c>
+      <c r="F381" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G381" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H381" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I381" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J381" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K381" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L381" s="5">
+        <v>0</v>
+      </c>
+      <c r="M381" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N381" s="4"/>
+    </row>
+    <row r="382" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A382" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D382" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E382" s="4">
+        <v>1.94</v>
+      </c>
+      <c r="F382" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G382" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H382" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I382" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J382" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K382" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L382" s="5">
+        <v>0</v>
+      </c>
+      <c r="M382" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N382" s="7" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="383" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A383" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B383" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="C383" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D383" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E383" s="4">
+        <v>4.07</v>
+      </c>
+      <c r="F383" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G383" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H383" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I383" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J383" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K383" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L383" s="5">
+        <v>0</v>
+      </c>
+      <c r="M383" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N383" s="4"/>
+    </row>
+    <row r="384" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A384" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="C384" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D384" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="E384" s="4">
+        <v>5.71</v>
+      </c>
+      <c r="F384" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G384" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H384" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I384" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J384" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K384" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L384" s="5">
+        <v>0</v>
+      </c>
+      <c r="M384" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N384" s="7" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="385" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A385" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="C385" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D385" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E385" s="4">
+        <v>4.83</v>
+      </c>
+      <c r="F385" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G385" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H385" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I385" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J385" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K385" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L385" s="5">
+        <v>0</v>
+      </c>
+      <c r="M385" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N385" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="386" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A386" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B386" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="C386" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D386" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="E386" s="4">
+        <v>3.77</v>
+      </c>
+      <c r="F386" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G386" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H386" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I386" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J386" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K386" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L386" s="5">
+        <v>0</v>
+      </c>
+      <c r="M386" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N386" s="4"/>
+    </row>
+    <row r="387" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A387" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B387" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="C387" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D387" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="E387" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="F387" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G387" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H387" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I387" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J387" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K387" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L387" s="5">
+        <v>0</v>
+      </c>
+      <c r="M387" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N387" s="39" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="388" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A388" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B388" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="C388" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D388" s="4">
+        <v>4</v>
+      </c>
+      <c r="E388" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="F388" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G388" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H388" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I388" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J388" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K388" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L388" s="5">
+        <v>0</v>
+      </c>
+      <c r="M388" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N388" s="4"/>
+    </row>
+    <row r="389" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A389" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B389" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C389" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D389" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="E389" s="4">
+        <v>1.82</v>
+      </c>
+      <c r="F389" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G389" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H389" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I389" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J389" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K389" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L389" s="5">
+        <v>0</v>
+      </c>
+      <c r="M389" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N389" s="4" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="390" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A390" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B390" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C390" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D390" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="E390" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="F390" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G390" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H390" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I390" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J390" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K390" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L390" s="5">
+        <v>0</v>
+      </c>
+      <c r="M390" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N390" s="4"/>
+    </row>
+    <row r="391" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A391" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B391" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C391" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D391" s="4">
+        <v>5.9</v>
+      </c>
+      <c r="E391" s="4">
+        <v>6.16</v>
+      </c>
+      <c r="F391" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G391" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H391" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I391" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J391" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K391" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L391" s="5">
+        <v>0</v>
+      </c>
+      <c r="M391" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N391" s="7" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="392" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A392" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B392" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="C392" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D392" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E392" s="4">
+        <v>2.33</v>
+      </c>
+      <c r="F392" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G392" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H392" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I392" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J392" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K392" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L392" s="5">
+        <v>0</v>
+      </c>
+      <c r="M392" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N392" s="4"/>
+    </row>
+    <row r="393" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A393" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B393" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="C393" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D393" s="4">
+        <v>4</v>
+      </c>
+      <c r="E393" s="4">
+        <v>2.1</v>
+      </c>
+      <c r="F393" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G393" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H393" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I393" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J393" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K393" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L393" s="5">
+        <v>0</v>
+      </c>
+      <c r="M393" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N393" s="7" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="394" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A394" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B394" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="C394" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D394" s="4">
+        <v>5.6</v>
+      </c>
+      <c r="E394" s="4">
+        <v>5.36</v>
+      </c>
+      <c r="F394" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G394" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H394" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I394" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J394" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K394" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L394" s="5">
+        <v>0</v>
+      </c>
+      <c r="M394" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N394" s="7" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="395" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A395" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B395" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="C395" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D395" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E395" s="4">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="F395" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G395" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H395" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I395" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J395" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K395" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L395" s="5">
+        <v>0</v>
+      </c>
+      <c r="M395" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N395" s="7" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="396" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A396" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="C396" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D396" s="4">
+        <v>4</v>
+      </c>
+      <c r="E396" s="4">
+        <v>1.81</v>
+      </c>
+      <c r="F396" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G396" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H396" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I396" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J396" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K396" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L396" s="5">
+        <v>0</v>
+      </c>
+      <c r="M396" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N396" s="7" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="397" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A397" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B397" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C397" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D397" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="E397" s="4">
+        <v>3.52</v>
+      </c>
+      <c r="F397" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G397" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H397" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I397" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J397" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K397" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L397" s="5">
+        <v>0</v>
+      </c>
+      <c r="M397" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N397" s="39" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="398" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A398" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B398" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="C398" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D398" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="E398" s="4">
+        <v>4.21</v>
+      </c>
+      <c r="F398" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G398" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H398" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I398" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J398" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K398" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L398" s="5">
+        <v>0</v>
+      </c>
+      <c r="M398" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N398" s="4"/>
+    </row>
+    <row r="399" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A399" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B399" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="C399" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D399" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="E399" s="4">
+        <v>1.82</v>
+      </c>
+      <c r="F399" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G399" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H399" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I399" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J399" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K399" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L399" s="5">
+        <v>0</v>
+      </c>
+      <c r="M399" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N399" s="4"/>
+    </row>
+    <row r="400" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A400" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B400" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C400" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D400" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="E400" s="4">
+        <v>5.15</v>
+      </c>
+      <c r="F400" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G400" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H400" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I400" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J400" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K400" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L400" s="5">
+        <v>0</v>
+      </c>
+      <c r="M400" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N400" s="40" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="401" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A401" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B401" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C401" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D401" s="4">
+        <v>5.6</v>
+      </c>
+      <c r="E401" s="4">
+        <v>5.04</v>
+      </c>
+      <c r="F401" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G401" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H401" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I401" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J401" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K401" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L401" s="5">
+        <v>0</v>
+      </c>
+      <c r="M401" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N401" s="4"/>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A402" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B402" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="C402" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D402" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="E402" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F402" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G402" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H402" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I402" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J402" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K402" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L402" s="5">
+        <v>0</v>
+      </c>
+      <c r="M402" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N402" s="39" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A403" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B403" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C403" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D403" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E403" s="4">
+        <v>2.33</v>
+      </c>
+      <c r="F403" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G403" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H403" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I403" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J403" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K403" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L403" s="5">
+        <v>0</v>
+      </c>
+      <c r="M403" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N403" s="39" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A404" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B404" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="C404" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D404" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E404" s="4">
+        <v>2.92</v>
+      </c>
+      <c r="F404" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G404" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H404" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I404" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J404" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K404" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L404" s="5">
+        <v>0</v>
+      </c>
+      <c r="M404" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N404" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A405" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B405" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="C405" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D405" s="4">
+        <v>5</v>
+      </c>
+      <c r="E405" s="4">
+        <v>3.57</v>
+      </c>
+      <c r="F405" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G405" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H405" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I405" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J405" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K405" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L405" s="5">
+        <v>0</v>
+      </c>
+      <c r="M405" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N405" s="4"/>
+    </row>
+    <row r="406" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A406" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B406" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="C406" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D406" s="4">
+        <v>5</v>
+      </c>
+      <c r="E406" s="4">
+        <v>2.84</v>
+      </c>
+      <c r="F406" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G406" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H406" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I406" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J406" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K406" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L406" s="5">
+        <v>0</v>
+      </c>
+      <c r="M406" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N406" s="4" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="407" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A407" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B407" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="C407" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D407" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E407" s="4">
+        <v>2</v>
+      </c>
+      <c r="F407" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="G407" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H407" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I407" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="J407" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K407" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L407" s="5">
+        <v>0</v>
+      </c>
+      <c r="M407" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N407" s="4"/>
+    </row>
+    <row r="408" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A408" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B408" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="C408" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D408" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="E408" s="4">
+        <v>2.23</v>
+      </c>
+      <c r="F408" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="G408" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H408" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I408" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="J408" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K408" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L408" s="5">
+        <v>0</v>
+      </c>
+      <c r="M408" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N408" s="4"/>
+    </row>
+    <row r="409" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A409" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B409" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="C409" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D409" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="E409" s="4">
+        <v>3.94</v>
+      </c>
+      <c r="F409" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="G409" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H409" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I409" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="J409" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K409" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L409" s="5">
+        <v>0</v>
+      </c>
+      <c r="M409" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N409" s="4"/>
+    </row>
+    <row r="410" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A410" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B410" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="C410" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D410" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="E410" s="4">
+        <v>2.08</v>
+      </c>
+      <c r="F410" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G410" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H410" s="6">
+        <v>46316</v>
+      </c>
+      <c r="I410" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J410" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K410" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L410" s="5">
+        <v>0</v>
+      </c>
+      <c r="M410" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N410" s="39" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="411" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A411" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B411" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="C411" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D411" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="E411" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F411" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="G411" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H411" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I411" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="J411" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K411" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L411" s="5">
+        <v>0</v>
+      </c>
+      <c r="M411" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N411" s="7" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="412" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A412" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B412" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="C412" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D412" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E412" s="4">
+        <v>2.48</v>
+      </c>
+      <c r="F412" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="G412" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H412" s="6">
+        <v>46311</v>
+      </c>
+      <c r="I412" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="J412" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K412" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L412" s="5">
+        <v>0</v>
+      </c>
+      <c r="M412" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N412" s="4"/>
+    </row>
+    <row r="413" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A413" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B413" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="C413" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D413" s="4">
+        <v>5.6</v>
+      </c>
+      <c r="E413" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F413" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="G413" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H413" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I413" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="J413" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K413" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L413" s="5">
+        <v>0</v>
+      </c>
+      <c r="M413" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N413" s="7" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="414" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A414" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B414" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="C414" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D414" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="E414" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F414" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G414" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H414" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I414" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J414" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K414" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L414" s="5">
+        <v>0</v>
+      </c>
+      <c r="M414" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N414" s="4"/>
+    </row>
+    <row r="415" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A415" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B415" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="C415" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D415" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="E415" s="4">
+        <v>3.93</v>
+      </c>
+      <c r="F415" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G415" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H415" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I415" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J415" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K415" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L415" s="5">
+        <v>0</v>
+      </c>
+      <c r="M415" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N415" s="4"/>
+    </row>
+    <row r="416" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A416" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B416" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C416" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D416" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="E416" s="4">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="F416" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G416" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H416" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I416" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J416" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K416" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L416" s="5">
+        <v>0</v>
+      </c>
+      <c r="M416" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N416" s="4" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="417" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A417" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B417" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="C417" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D417" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E417" s="4">
+        <v>2.02</v>
+      </c>
+      <c r="F417" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G417" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H417" s="6">
+        <v>46311</v>
+      </c>
+      <c r="I417" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J417" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K417" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L417" s="5">
+        <v>0</v>
+      </c>
+      <c r="M417" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N417" s="4"/>
+    </row>
+    <row r="418" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A418" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B418" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="C418" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D418" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="E418" s="4">
+        <v>3.87</v>
+      </c>
+      <c r="F418" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G418" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H418" s="6">
+        <v>46311</v>
+      </c>
+      <c r="I418" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J418" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K418" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L418" s="5">
+        <v>0</v>
+      </c>
+      <c r="M418" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N418" s="4"/>
+    </row>
+    <row r="419" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A419" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B419" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="C419" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D419" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="E419" s="4">
+        <v>4.88</v>
+      </c>
+      <c r="F419" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G419" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H419" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I419" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J419" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K419" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L419" s="5">
+        <v>0</v>
+      </c>
+      <c r="M419" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N419" s="7" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="420" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A420" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B420" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="C420" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D420" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E420" s="4">
+        <v>4.76</v>
+      </c>
+      <c r="F420" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G420" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H420" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I420" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J420" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K420" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L420" s="5">
+        <v>0</v>
+      </c>
+      <c r="M420" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N420" s="4"/>
+    </row>
+    <row r="421" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A421" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B421" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="C421" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D421" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="E421" s="4">
+        <v>3.97</v>
+      </c>
+      <c r="F421" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G421" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H421" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I421" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J421" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K421" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L421" s="5">
+        <v>0</v>
+      </c>
+      <c r="M421" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N421" s="4"/>
+    </row>
+    <row r="422" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A422" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B422" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="C422" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D422" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="E422" s="4">
+        <v>1.76</v>
+      </c>
+      <c r="F422" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G422" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H422" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I422" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J422" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K422" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L422" s="5">
+        <v>0</v>
+      </c>
+      <c r="M422" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N422" s="4"/>
+    </row>
+    <row r="423" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A423" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B423" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="C423" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D423" s="4">
+        <v>4</v>
+      </c>
+      <c r="E423" s="4">
+        <v>1.64</v>
+      </c>
+      <c r="F423" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G423" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H423" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I423" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J423" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K423" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L423" s="5">
+        <v>0</v>
+      </c>
+      <c r="M423" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N423" s="4"/>
+    </row>
+    <row r="424" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A424" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B424" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="C424" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D424" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="E424" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F424" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G424" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H424" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I424" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J424" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K424" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L424" s="5">
+        <v>0</v>
+      </c>
+      <c r="M424" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N424" s="4"/>
+    </row>
+    <row r="425" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A425" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B425" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="C425" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D425" s="4">
+        <v>5.6</v>
+      </c>
+      <c r="E425" s="4">
+        <v>4.46</v>
+      </c>
+      <c r="F425" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G425" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H425" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I425" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J425" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K425" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L425" s="5">
+        <v>0</v>
+      </c>
+      <c r="M425" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N425" s="4"/>
+    </row>
+    <row r="426" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A426" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B426" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="C426" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D426" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="E426" s="4">
+        <v>2.11</v>
+      </c>
+      <c r="F426" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G426" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H426" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I426" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J426" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K426" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L426" s="5">
+        <v>0</v>
+      </c>
+      <c r="M426" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N426" s="7" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="427" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A427" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B427" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="C427" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D427" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="E427" s="4">
+        <v>4.76</v>
+      </c>
+      <c r="F427" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G427" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H427" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I427" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J427" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K427" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L427" s="5">
+        <v>0</v>
+      </c>
+      <c r="M427" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N427" s="4"/>
+    </row>
+    <row r="428" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A428" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B428" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="C428" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D428" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="E428" s="4">
+        <v>4.26</v>
+      </c>
+      <c r="F428" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G428" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H428" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I428" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J428" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K428" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L428" s="5">
+        <v>0</v>
+      </c>
+      <c r="M428" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N428" s="4"/>
+    </row>
+    <row r="429" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A429" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B429" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="C429" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D429" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="E429" s="4">
+        <v>2.41</v>
+      </c>
+      <c r="F429" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G429" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H429" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I429" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J429" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K429" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L429" s="5">
+        <v>0</v>
+      </c>
+      <c r="M429" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N429" s="4"/>
+    </row>
+    <row r="430" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A430" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B430" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="C430" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D430" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="E430" s="4">
+        <v>2.64</v>
+      </c>
+      <c r="F430" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G430" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H430" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I430" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J430" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K430" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L430" s="5">
+        <v>0</v>
+      </c>
+      <c r="M430" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N430" s="4" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="431" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A431" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D431" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="E431" s="4">
+        <v>2.12</v>
+      </c>
+      <c r="F431" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G431" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H431" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I431" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J431" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K431" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L431" s="5">
+        <v>0</v>
+      </c>
+      <c r="M431" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N431" s="4"/>
+    </row>
+    <row r="432" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A432" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B432" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="C432" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D432" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="E432" s="4">
+        <v>1.77</v>
+      </c>
+      <c r="F432" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G432" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H432" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I432" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J432" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K432" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L432" s="5">
+        <v>0</v>
+      </c>
+      <c r="M432" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N432" s="4" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="433" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A433" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="C433" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D433" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="E433" s="4">
+        <v>1.96</v>
+      </c>
+      <c r="F433" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G433" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H433" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I433" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J433" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K433" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L433" s="5">
+        <v>0</v>
+      </c>
+      <c r="M433" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N433" s="4"/>
+    </row>
+    <row r="434" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A434" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B434" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="C434" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D434" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E434" s="4">
+        <v>5.39</v>
+      </c>
+      <c r="F434" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G434" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H434" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I434" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J434" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K434" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L434" s="5">
+        <v>0</v>
+      </c>
+      <c r="M434" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N434" s="4"/>
+    </row>
+    <row r="435" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A435" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B435" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="C435" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D435" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E435" s="4">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="F435" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G435" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H435" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I435" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J435" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K435" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L435" s="5">
+        <v>0</v>
+      </c>
+      <c r="M435" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N435" s="4"/>
+    </row>
+    <row r="436" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A436" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B436" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="C436" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D436" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="E436" s="4">
+        <v>3.29</v>
+      </c>
+      <c r="F436" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G436" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H436" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I436" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J436" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K436" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L436" s="5">
+        <v>0</v>
+      </c>
+      <c r="M436" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N436" s="4"/>
+    </row>
+    <row r="437" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A437" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B437" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="C437" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D437" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="E437" s="4">
+        <v>5.13</v>
+      </c>
+      <c r="F437" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G437" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H437" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I437" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J437" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K437" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L437" s="5">
+        <v>0</v>
+      </c>
+      <c r="M437" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N437" s="4"/>
+    </row>
+    <row r="438" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A438" s="8">
+        <v>46190</v>
+      </c>
+      <c r="B438" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="C438" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D438" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="E438" s="9">
+        <v>4.74</v>
+      </c>
+      <c r="F438" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G438" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H438" s="11">
+        <v>46313</v>
+      </c>
+      <c r="I438" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J438" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K438" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L438" s="10">
+        <v>3</v>
+      </c>
+      <c r="M438" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N438" s="9" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="439" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A439" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B439" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="C439" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D439" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="E439" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="F439" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G439" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H439" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I439" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J439" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K439" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L439" s="5">
+        <v>0</v>
+      </c>
+      <c r="M439" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N439" s="4"/>
+    </row>
+    <row r="440" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A440" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B440" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="C440" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D440" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="E440" s="4">
+        <v>4.93</v>
+      </c>
+      <c r="F440" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G440" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H440" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I440" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J440" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K440" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L440" s="5">
+        <v>0</v>
+      </c>
+      <c r="M440" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N440" s="4" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="441" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A441" s="8">
+        <v>46190</v>
+      </c>
+      <c r="B441" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="C441" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D441" s="9">
+        <v>5.6</v>
+      </c>
+      <c r="E441" s="9">
+        <v>4.88</v>
+      </c>
+      <c r="F441" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G441" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H441" s="11">
+        <v>46313</v>
+      </c>
+      <c r="I441" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J441" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K441" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L441" s="10">
+        <v>2</v>
+      </c>
+      <c r="M441" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N441" s="9" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="442" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A442" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B442" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C442" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D442" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="E442" s="4">
+        <v>5.64</v>
+      </c>
+      <c r="F442" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G442" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H442" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I442" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J442" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K442" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L442" s="5">
+        <v>0</v>
+      </c>
+      <c r="M442" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N442" s="39" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="443" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A443" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B443" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="C443" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D443" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E443" s="4">
+        <v>2.1</v>
+      </c>
+      <c r="F443" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G443" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H443" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I443" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J443" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K443" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L443" s="5">
+        <v>0</v>
+      </c>
+      <c r="M443" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N443" s="4"/>
+    </row>
+    <row r="444" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A444" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B444" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="C444" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D444" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E444" s="4">
+        <v>4.66</v>
+      </c>
+      <c r="F444" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G444" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H444" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I444" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J444" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K444" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L444" s="5">
+        <v>0</v>
+      </c>
+      <c r="M444" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N444" s="4" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="445" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A445" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B445" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="C445" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D445" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="E445" s="4">
+        <v>5.18</v>
+      </c>
+      <c r="F445" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G445" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H445" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I445" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J445" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K445" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L445" s="5">
+        <v>0</v>
+      </c>
+      <c r="M445" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N445" s="39" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="446" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A446" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B446" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="C446" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D446" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="E446" s="4">
+        <v>2.38</v>
+      </c>
+      <c r="F446" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G446" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H446" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I446" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J446" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K446" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L446" s="5">
+        <v>0</v>
+      </c>
+      <c r="M446" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N446" s="4"/>
+    </row>
+    <row r="447" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A447" s="8">
+        <v>46190</v>
+      </c>
+      <c r="B447" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="C447" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D447" s="9">
+        <v>6</v>
+      </c>
+      <c r="E447" s="9">
+        <v>5.92</v>
+      </c>
+      <c r="F447" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G447" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H447" s="11">
+        <v>46314</v>
+      </c>
+      <c r="I447" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J447" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K447" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L447" s="10">
+        <v>121</v>
+      </c>
+      <c r="M447" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N447" s="9" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="448" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A448" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B448" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="C448" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D448" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="E448" s="4">
+        <v>1.92</v>
+      </c>
+      <c r="F448" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G448" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H448" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I448" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J448" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K448" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L448" s="5">
+        <v>0</v>
+      </c>
+      <c r="M448" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N448" s="4"/>
+    </row>
+    <row r="449" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A449" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B449" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="C449" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D449" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E449" s="4">
+        <v>2.42</v>
+      </c>
+      <c r="F449" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G449" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H449" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I449" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J449" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K449" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L449" s="5">
+        <v>0</v>
+      </c>
+      <c r="M449" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N449" s="4"/>
+    </row>
+    <row r="450" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A450" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B450" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="C450" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D450" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="E450" s="4">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="F450" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G450" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H450" s="6">
+        <v>46315</v>
+      </c>
+      <c r="I450" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J450" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K450" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L450" s="5">
+        <v>0</v>
+      </c>
+      <c r="M450" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N450" s="4"/>
+    </row>
+    <row r="451" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A451" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B451" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="C451" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D451" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E451" s="4">
+        <v>1.77</v>
+      </c>
+      <c r="F451" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G451" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H451" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I451" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J451" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K451" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L451" s="5">
+        <v>0</v>
+      </c>
+      <c r="M451" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N451" s="4"/>
+    </row>
+    <row r="452" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A452" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B452" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="C452" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D452" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E452" s="4">
+        <v>2.36</v>
+      </c>
+      <c r="F452" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G452" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H452" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I452" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J452" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K452" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L452" s="5">
+        <v>0</v>
+      </c>
+      <c r="M452" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N452" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="453" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A453" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B453" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="C453" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D453" s="9">
+        <v>5.8</v>
+      </c>
+      <c r="E453" s="9">
+        <v>5.33</v>
+      </c>
+      <c r="F453" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G453" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H453" s="11">
+        <v>46313</v>
+      </c>
+      <c r="I453" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J453" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K453" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L453" s="10">
+        <v>4</v>
+      </c>
+      <c r="M453" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N453" s="9" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="454" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A454" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B454" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="C454" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D454" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E454" s="4">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="F454" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G454" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H454" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I454" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J454" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K454" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L454" s="5">
+        <v>0</v>
+      </c>
+      <c r="M454" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N454" s="4"/>
+    </row>
+    <row r="455" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A455" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B455" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="C455" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D455" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E455" s="4">
+        <v>1.97</v>
+      </c>
+      <c r="F455" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G455" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H455" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I455" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J455" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K455" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L455" s="5">
+        <v>0</v>
+      </c>
+      <c r="M455" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N455" s="4"/>
+    </row>
+    <row r="456" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A456" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B456" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="C456" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D456" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="E456" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F456" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G456" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H456" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I456" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J456" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K456" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L456" s="5">
+        <v>0</v>
+      </c>
+      <c r="M456" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N456" s="7" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="457" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A457" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B457" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="C457" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D457" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E457" s="4">
+        <v>2.46</v>
+      </c>
+      <c r="F457" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G457" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H457" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I457" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J457" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K457" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L457" s="5">
+        <v>0</v>
+      </c>
+      <c r="M457" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N457" s="4"/>
+    </row>
+    <row r="458" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A458" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B458" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="C458" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D458" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="E458" s="4">
+        <v>2.46</v>
+      </c>
+      <c r="F458" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G458" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H458" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I458" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J458" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K458" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L458" s="5">
+        <v>0</v>
+      </c>
+      <c r="M458" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N458" s="7" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="459" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A459" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B459" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="C459" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D459" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="E459" s="4">
+        <v>4.79</v>
+      </c>
+      <c r="F459" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G459" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H459" s="6">
+        <v>46314</v>
+      </c>
+      <c r="I459" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J459" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K459" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L459" s="5">
+        <v>0</v>
+      </c>
+      <c r="M459" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N459" s="4"/>
+    </row>
+    <row r="460" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A460" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B460" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="C460" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D460" s="4">
+        <v>4</v>
+      </c>
+      <c r="E460" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="F460" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G460" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H460" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I460" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J460" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K460" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L460" s="5">
+        <v>0</v>
+      </c>
+      <c r="M460" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N460" s="4"/>
+    </row>
+    <row r="461" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A461" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B461" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="C461" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D461" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="E461" s="4">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="F461" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G461" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H461" s="6">
+        <v>46313</v>
+      </c>
+      <c r="I461" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J461" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K461" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L461" s="5">
+        <v>0</v>
+      </c>
+      <c r="M461" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N461" s="4"/>
+    </row>
+    <row r="462" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A462" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B462" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="C462" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D462" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="E462" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F462" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G462" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H462" s="4"/>
+      <c r="I462" s="4"/>
+      <c r="J462" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="463" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A463" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B463" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="C463" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D463" s="4">
+        <v>5.9</v>
+      </c>
+      <c r="E463" s="4">
+        <v>6.23</v>
+      </c>
+      <c r="F463" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G463" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H463" s="4"/>
+      <c r="I463" s="4"/>
+      <c r="J463" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="464" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A464" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B464" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="C464" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D464" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="E464" s="4">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="F464" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G464" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H464" s="4"/>
+      <c r="I464" s="4"/>
+      <c r="J464" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="465" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A465" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B465" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C465" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="D465" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="E465" s="4">
+        <v>1.56</v>
+      </c>
+      <c r="F465" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G465" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H465" s="4"/>
+      <c r="I465" s="4"/>
+      <c r="J465" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="466" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A466" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B466" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="C466" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D466" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="E466" s="4">
+        <v>1.18</v>
+      </c>
+      <c r="F466" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G466" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H466" s="4"/>
+      <c r="I466" s="4"/>
+    </row>
+    <row r="467" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A467" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B467" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="C467" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D467" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="E467" s="4">
+        <v>2.21</v>
+      </c>
+      <c r="F467" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G467" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="468" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A468" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B468" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="C468" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D468" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="E468" s="4">
+        <v>5.48</v>
+      </c>
+      <c r="F468" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G468" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="469" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A469" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B469" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="C469" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D469" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E469" s="4">
+        <v>2.94</v>
+      </c>
+      <c r="F469" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G469" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="470" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A470" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B470" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C470" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="D470" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="E470" s="4">
+        <v>2.72</v>
+      </c>
+      <c r="F470" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G470" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="471" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A471" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B471" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C471" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D471" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="E471" s="4">
+        <v>6.13</v>
+      </c>
+      <c r="F471" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G471" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="472" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A472" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B472" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="C472" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D472" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="E472" s="4">
+        <v>2.72</v>
+      </c>
+      <c r="F472" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G472" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="473" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A473" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B473" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="C473" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D473" s="4">
+        <v>4</v>
+      </c>
+      <c r="E473" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="F473" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G473" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="474" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A474" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B474" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="C474" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D474" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="E474" s="4">
+        <v>5.09</v>
+      </c>
+      <c r="F474" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G474" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="475" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A475" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B475" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="C475" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D475" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E475" s="4">
+        <v>2.15</v>
+      </c>
+      <c r="F475" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G475" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="476" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A476" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B476" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="C476" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D476" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E476" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="F476" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G476" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="477" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A477" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B477" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="C477" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D477" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="E477" s="4">
+        <v>5.64</v>
+      </c>
+      <c r="F477" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G477" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="478" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A478" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B478" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="C478" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D478" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="E478" s="4">
+        <v>5.41</v>
+      </c>
+      <c r="F478" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G478" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="479" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A479" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B479" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="C479" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D479" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E479" s="4">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="F479" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G479" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="480" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A480" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B480" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="C480" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D480" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="E480" s="4">
+        <v>2.87</v>
+      </c>
+      <c r="F480" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G480" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A481" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B481" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="C481" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D481" s="4">
+        <v>4</v>
+      </c>
+      <c r="E481" s="4">
+        <v>1.82</v>
+      </c>
+      <c r="F481" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G481" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A482" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B482" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="C482" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D482" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="E482" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="F482" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G482" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A483" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B483" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="C483" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D483" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E483" s="4">
+        <v>3.03</v>
+      </c>
+      <c r="F483" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G483" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A484" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B484" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="C484" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D484" s="4">
+        <v>5.9</v>
+      </c>
+      <c r="E484" s="4">
+        <v>5.26</v>
+      </c>
+      <c r="F484" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G484" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A485" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B485" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="C485" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D485" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E485" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="F485" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G485" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A486" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B486" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C486" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D486" s="4">
+        <v>5.6</v>
+      </c>
+      <c r="E486" s="4">
+        <v>5.48</v>
+      </c>
+      <c r="F486" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G486" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A487" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B487" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C487" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D487" s="4">
+        <v>4</v>
+      </c>
+      <c r="E487" s="4">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="F487" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G487" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A488" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B488" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="C488" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D488" s="4">
+        <v>5</v>
+      </c>
+      <c r="E488" s="4">
+        <v>4.16</v>
+      </c>
+      <c r="F488" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G488" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A489" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B489" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C489" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D489" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="E489" s="4">
+        <v>2.77</v>
+      </c>
+      <c r="F489" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G489" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A490" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B490" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="C490" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D490" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E490" s="4">
+        <v>1.78</v>
+      </c>
+      <c r="F490" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G490" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A491" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B491" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="C491" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D491" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="E491" s="4">
+        <v>5.21</v>
+      </c>
+      <c r="F491" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G491" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A492" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B492" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="C492" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D492" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="E492" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="F492" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G492" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A493" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B493" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="C493" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D493" s="4">
+        <v>5.6</v>
+      </c>
+      <c r="E493" s="4">
+        <v>5.35</v>
+      </c>
+      <c r="F493" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G493" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A494" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B494" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="C494" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D494" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E494" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F494" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G494" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A495" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B495" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="C495" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D495" s="4">
+        <v>5.6</v>
+      </c>
+      <c r="E495" s="4">
+        <v>6.24</v>
+      </c>
+      <c r="F495" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G495" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A496" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B496" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="C496" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D496" s="4">
+        <v>4</v>
+      </c>
+      <c r="E496" s="4">
+        <v>1.71</v>
+      </c>
+      <c r="F496" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G496" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="497" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A497" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B497" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="C497" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D497" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="E497" s="4">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="F497" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G497" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="498" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A498" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B498" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C498" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D498" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E498" s="4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F498" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G498" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="499" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A499" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B499" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="C499" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D499" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E499" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="F499" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G499" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="500" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A500" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B500" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="C500" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D500" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="E500" s="4">
+        <v>1.65</v>
+      </c>
+      <c r="F500" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G500" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="501" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A501" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B501" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="C501" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D501" s="4">
+        <v>5</v>
+      </c>
+      <c r="E501" s="4">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F501" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G501" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="502" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A502" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B502" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="C502" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D502" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E502" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="F502" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G502" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="503" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A503" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B503" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="C503" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D503" s="4">
+        <v>4</v>
+      </c>
+      <c r="E503" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="F503" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G503" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="504" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A504" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B504" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C504" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D504" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="E504" s="4">
+        <v>5.55</v>
+      </c>
+      <c r="F504" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G504" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="505" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A505" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B505" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="C505" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D505" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="E505" s="4">
+        <v>1.38</v>
+      </c>
+      <c r="F505" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G505" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="506" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A506" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B506" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="C506" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D506" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E506" s="4">
+        <v>1.86</v>
+      </c>
+      <c r="F506" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G506" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="507" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A507" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B507" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="C507" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D507" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="E507" s="4">
+        <v>1.95</v>
+      </c>
+      <c r="F507" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G507" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="508" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A508" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B508" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="C508" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D508" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="E508" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="F508" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G508" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="509" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A509" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B509" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="C509" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D509" s="4">
+        <v>5.6</v>
+      </c>
+      <c r="E509" s="4">
+        <v>4.51</v>
+      </c>
+      <c r="F509" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G509" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="510" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A510" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B510" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="C510" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D510" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E510" s="4">
+        <v>3.69</v>
+      </c>
+      <c r="F510" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G510" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="511" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A511" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B511" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="C511" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D511" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="E511" s="4">
+        <v>4.97</v>
+      </c>
+      <c r="F511" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G511" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N511" s="4"/>
+    </row>
+    <row r="512" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A512" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B512" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="C512" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D512" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="E512" s="4">
+        <v>1.95</v>
+      </c>
+      <c r="F512" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G512" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N512" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="513" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A513" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B513" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="C513" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="D513" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="E513" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="F513" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G513" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N513" s="4"/>
+    </row>
+    <row r="514" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A514" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B514" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="C514" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="D514" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="E514" s="4">
+        <v>3.02</v>
+      </c>
+      <c r="F514" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G514" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N514" s="4"/>
+    </row>
+    <row r="515" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A515" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B515" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="C515" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D515" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="E515" s="4">
+        <v>1.95</v>
+      </c>
+      <c r="F515" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G515" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N515" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="516" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A516" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B516" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="C516" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D516" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E516" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="F516" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G516" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N516" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="517" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A517" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B517" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="C517" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D517" s="4">
+        <v>5.6</v>
+      </c>
+      <c r="E517" s="4">
+        <v>4.71</v>
+      </c>
+      <c r="F517" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G517" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N517" s="4"/>
+    </row>
+    <row r="518" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A518" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B518" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="C518" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D518" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="E518" s="4">
+        <v>7.14</v>
+      </c>
+      <c r="F518" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G518" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N518" s="4"/>
+    </row>
+    <row r="519" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A519" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B519" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="C519" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D519" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="E519" s="4">
+        <v>4.95</v>
+      </c>
+      <c r="F519" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G519" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N519" s="4"/>
+    </row>
+    <row r="520" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A520" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B520" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="C520" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D520" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E520" s="4">
+        <v>4.37</v>
+      </c>
+      <c r="F520" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G520" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N520" s="4"/>
+    </row>
+    <row r="521" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A521" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B521" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="C521" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D521" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="E521" s="4">
+        <v>4.71</v>
+      </c>
+      <c r="F521" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G521" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N521" s="4"/>
+    </row>
+    <row r="522" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A522" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B522" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="C522" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D522" s="4">
+        <v>5.6</v>
+      </c>
+      <c r="E522" s="4">
+        <v>5.84</v>
+      </c>
+      <c r="F522" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G522" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N522" s="4"/>
+    </row>
+    <row r="523" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A523" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B523" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="C523" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D523" s="4">
+        <v>5.9</v>
+      </c>
+      <c r="E523" s="4">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F523" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G523" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N523" s="4"/>
+    </row>
+    <row r="524" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A524" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B524" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="C524" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D524" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="E524" s="4">
+        <v>4.54</v>
+      </c>
+      <c r="F524" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G524" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N524" s="4"/>
+    </row>
+    <row r="525" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A525" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B525" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="C525" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D525" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="E525" s="4">
+        <v>4.78</v>
+      </c>
+      <c r="F525" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G525" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N525" s="4"/>
+    </row>
+    <row r="526" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A526" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B526" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="C526" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D526" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E526" s="4">
+        <v>5.51</v>
+      </c>
+      <c r="F526" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G526" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N526" s="4"/>
+    </row>
+    <row r="527" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A527" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B527" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="C527" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D527" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="E527" s="4">
+        <v>4.32</v>
+      </c>
+      <c r="F527" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G527" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N527" s="4"/>
+    </row>
+    <row r="528" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A528" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B528" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="C528" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D528" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E528" s="4">
+        <v>2.58</v>
+      </c>
+      <c r="F528" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G528" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N528" s="4"/>
+    </row>
+    <row r="529" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A529" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B529" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="C529" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D529" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="E529" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="F529" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G529" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N529" s="4"/>
+    </row>
+    <row r="530" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A530" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B530" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="C530" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D530" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="E530" s="4">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="F530" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G530" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N530" s="4"/>
+    </row>
+    <row r="531" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A531" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B531" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="C531" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D531" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="E531" s="4">
+        <v>1.77</v>
+      </c>
+      <c r="F531" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G531" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N531" s="4"/>
+    </row>
+    <row r="532" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A532" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B532" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="C532" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D532" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="E532" s="4">
+        <v>4.82</v>
+      </c>
+      <c r="F532" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G532" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N532" s="4"/>
+    </row>
+    <row r="533" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A533" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B533" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="C533" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D533" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="E533" s="4">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="F533" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G533" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N533" s="4"/>
+    </row>
+    <row r="534" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A534" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B534" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="C534" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D534" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="E534" s="4">
+        <v>2.09</v>
+      </c>
+      <c r="F534" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G534" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N534" s="4"/>
+    </row>
+    <row r="535" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A535" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B535" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="C535" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D535" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E535" s="4">
+        <v>1.89</v>
+      </c>
+      <c r="F535" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G535" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N535" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="536" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A536" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B536" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="C536" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D536" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E536" s="4">
+        <v>2.38</v>
+      </c>
+      <c r="F536" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G536" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N536" s="4"/>
+    </row>
+    <row r="537" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A537" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B537" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="C537" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D537" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="E537" s="4">
+        <v>2.12</v>
+      </c>
+      <c r="F537" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G537" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N537" s="4"/>
+    </row>
+    <row r="538" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A538" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B538" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="C538" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D538" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="E538" s="4">
+        <v>1.42</v>
+      </c>
+      <c r="F538" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G538" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N538" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="539" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A539" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B539" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C539" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D539" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E539" s="4">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="F539" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G539" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N539" s="4"/>
+    </row>
+    <row r="540" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A540" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B540" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="C540" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D540" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E540" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="F540" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G540" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N540" s="4"/>
+    </row>
+    <row r="541" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A541" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B541" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="C541" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D541" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="E541" s="4">
+        <v>2.98</v>
+      </c>
+      <c r="F541" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G541" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N541" s="4"/>
+    </row>
+    <row r="542" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A542" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B542" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="C542" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D542" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="E542" s="4">
+        <v>2.08</v>
+      </c>
+      <c r="F542" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G542" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N542" s="4"/>
+    </row>
+    <row r="543" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A543" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B543" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="C543" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D543" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E543" s="4">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="F543" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G543" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N543" s="4"/>
+    </row>
+    <row r="544" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A544" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B544" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="C544" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D544" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E544" s="4">
+        <v>1.88</v>
+      </c>
+      <c r="F544" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G544" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N544" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="545" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A545" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B545" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="C545" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D545" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E545" s="4">
+        <v>2.38</v>
+      </c>
+      <c r="F545" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G545" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N545" s="4"/>
+    </row>
+    <row r="546" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A546" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B546" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="C546" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="D546" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E546" s="4">
+        <v>0.77</v>
+      </c>
+      <c r="F546" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G546" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N546" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="547" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A547" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B547" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="C547" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D547" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E547" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="F547" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G547" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N547" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="548" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A548" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B548" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="C548" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D548" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="E548" s="4">
+        <v>1.23</v>
+      </c>
+      <c r="F548" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G548" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N548" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="549" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A549" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B549" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="C549" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D549" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="E549" s="4">
+        <v>4.54</v>
+      </c>
+      <c r="F549" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G549" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="550" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A550" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B550" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="C550" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D550" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="E550" s="4">
+        <v>2.27</v>
+      </c>
+      <c r="F550" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G550" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="551" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A551" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B551" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="C551" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D551" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E551" s="4">
+        <v>2.41</v>
+      </c>
+      <c r="F551" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G551" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Herpeton Anole Data.xlsx
+++ b/Herpeton Anole Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasminekesselring/Desktop/Anole_Biometry_Practice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F72B804-6E6D-684B-B4FD-DD42D5646548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705886DC-3460-7649-8F9D-057971E7131D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{5183197B-93B4-694E-BC06-28ADA81A1872}"/>
+    <workbookView xWindow="500" yWindow="660" windowWidth="18660" windowHeight="17160" xr2:uid="{5183197B-93B4-694E-BC06-28ADA81A1872}"/>
   </bookViews>
   <sheets>
     <sheet name="Anole Master Sheet" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4305" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4391" uniqueCount="735">
   <si>
     <t>Collection_Date</t>
   </si>
@@ -2945,7 +2945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3903B938-DE2F-DB42-860C-BE543646DADC}">
-  <dimension ref="A1:N551"/>
+  <dimension ref="A1:N564"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="19" customWidth="1"/>
@@ -22929,6 +22929,9 @@
       </c>
       <c r="H466" s="4"/>
       <c r="I466" s="4"/>
+      <c r="J466" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A467" s="3">
@@ -22952,6 +22955,9 @@
       <c r="G467" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J467" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A468" s="3">
@@ -22975,6 +22981,9 @@
       <c r="G468" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J468" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A469" s="3">
@@ -22998,6 +23007,9 @@
       <c r="G469" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J469" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A470" s="3">
@@ -23021,6 +23033,9 @@
       <c r="G470" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J470" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A471" s="3">
@@ -23044,6 +23059,9 @@
       <c r="G471" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J471" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A472" s="3">
@@ -23067,6 +23085,9 @@
       <c r="G472" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J472" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A473" s="3">
@@ -23090,6 +23111,9 @@
       <c r="G473" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J473" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A474" s="3">
@@ -23113,6 +23137,9 @@
       <c r="G474" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J474" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A475" s="3">
@@ -23136,6 +23163,9 @@
       <c r="G475" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J475" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A476" s="3">
@@ -23159,6 +23189,9 @@
       <c r="G476" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J476" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A477" s="3">
@@ -23182,6 +23215,9 @@
       <c r="G477" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J477" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A478" s="3">
@@ -23205,6 +23241,9 @@
       <c r="G478" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J478" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A479" s="3">
@@ -23228,6 +23267,9 @@
       <c r="G479" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J479" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A480" s="3">
@@ -23251,8 +23293,11 @@
       <c r="G480" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J480" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="481" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A481" s="3">
         <v>46100</v>
       </c>
@@ -23274,8 +23319,11 @@
       <c r="G481" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J481" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="482" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A482" s="3">
         <v>46100</v>
       </c>
@@ -23297,8 +23345,11 @@
       <c r="G482" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J482" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="483" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A483" s="3">
         <v>46100</v>
       </c>
@@ -23320,8 +23371,11 @@
       <c r="G483" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J483" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="484" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A484" s="3">
         <v>46100</v>
       </c>
@@ -23343,8 +23397,11 @@
       <c r="G484" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J484" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="485" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A485" s="3">
         <v>46100</v>
       </c>
@@ -23366,8 +23423,11 @@
       <c r="G485" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J485" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="486" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A486" s="3">
         <v>46100</v>
       </c>
@@ -23389,8 +23449,11 @@
       <c r="G486" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J486" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="487" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A487" s="3">
         <v>46100</v>
       </c>
@@ -23412,8 +23475,11 @@
       <c r="G487" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J487" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="488" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A488" s="3">
         <v>46100</v>
       </c>
@@ -23435,8 +23501,11 @@
       <c r="G488" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J488" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="489" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A489" s="3">
         <v>46100</v>
       </c>
@@ -23458,8 +23527,11 @@
       <c r="G489" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J489" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="490" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A490" s="3">
         <v>46100</v>
       </c>
@@ -23481,8 +23553,11 @@
       <c r="G490" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J490" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="491" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A491" s="3">
         <v>46100</v>
       </c>
@@ -23504,8 +23579,11 @@
       <c r="G491" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J491" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="492" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A492" s="3">
         <v>46100</v>
       </c>
@@ -23527,8 +23605,11 @@
       <c r="G492" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J492" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="493" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A493" s="3">
         <v>46100</v>
       </c>
@@ -23550,8 +23631,11 @@
       <c r="G493" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J493" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="494" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A494" s="3">
         <v>46100</v>
       </c>
@@ -23573,8 +23657,11 @@
       <c r="G494" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J494" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="495" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A495" s="3">
         <v>46100</v>
       </c>
@@ -23596,8 +23683,11 @@
       <c r="G495" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J495" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="496" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A496" s="3">
         <v>46100</v>
       </c>
@@ -23618,6 +23708,9 @@
       </c>
       <c r="G496" s="4" t="s">
         <v>149</v>
+      </c>
+      <c r="J496" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="497" spans="1:14" x14ac:dyDescent="0.2">
@@ -23642,6 +23735,9 @@
       <c r="G497" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J497" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="498" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A498" s="3">
@@ -23665,6 +23761,9 @@
       <c r="G498" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J498" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="499" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A499" s="3">
@@ -23688,6 +23787,9 @@
       <c r="G499" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J499" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="500" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A500" s="3">
@@ -23711,6 +23813,9 @@
       <c r="G500" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J500" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="501" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A501" s="3">
@@ -23734,6 +23839,9 @@
       <c r="G501" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J501" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="502" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A502" s="3">
@@ -23757,6 +23865,9 @@
       <c r="G502" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J502" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="503" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A503" s="3">
@@ -23780,6 +23891,9 @@
       <c r="G503" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J503" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="504" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A504" s="3">
@@ -23803,6 +23917,9 @@
       <c r="G504" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J504" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="505" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A505" s="3">
@@ -23826,6 +23943,9 @@
       <c r="G505" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J505" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="506" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A506" s="3">
@@ -23849,6 +23969,9 @@
       <c r="G506" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J506" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="507" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A507" s="3">
@@ -23872,6 +23995,9 @@
       <c r="G507" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J507" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="508" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A508" s="3">
@@ -23895,6 +24021,9 @@
       <c r="G508" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J508" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="509" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A509" s="3">
@@ -23918,6 +24047,9 @@
       <c r="G509" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J509" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="510" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A510" s="3">
@@ -23941,6 +24073,9 @@
       <c r="G510" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J510" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="511" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A511" s="3">
@@ -23964,6 +24099,9 @@
       <c r="G511" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J511" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N511" s="4"/>
     </row>
     <row r="512" spans="1:14" x14ac:dyDescent="0.2">
@@ -23988,6 +24126,9 @@
       <c r="G512" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J512" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N512" s="4" t="s">
         <v>695</v>
       </c>
@@ -24014,6 +24155,9 @@
       <c r="G513" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J513" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N513" s="4"/>
     </row>
     <row r="514" spans="1:14" x14ac:dyDescent="0.2">
@@ -24038,6 +24182,9 @@
       <c r="G514" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J514" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N514" s="4"/>
     </row>
     <row r="515" spans="1:14" x14ac:dyDescent="0.2">
@@ -24062,6 +24209,9 @@
       <c r="G515" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J515" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N515" s="4" t="s">
         <v>695</v>
       </c>
@@ -24088,6 +24238,9 @@
       <c r="G516" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J516" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N516" s="4" t="s">
         <v>695</v>
       </c>
@@ -24114,6 +24267,9 @@
       <c r="G517" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J517" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N517" s="4"/>
     </row>
     <row r="518" spans="1:14" x14ac:dyDescent="0.2">
@@ -24138,6 +24294,9 @@
       <c r="G518" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J518" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N518" s="4"/>
     </row>
     <row r="519" spans="1:14" x14ac:dyDescent="0.2">
@@ -24162,6 +24321,9 @@
       <c r="G519" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J519" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N519" s="4"/>
     </row>
     <row r="520" spans="1:14" x14ac:dyDescent="0.2">
@@ -24186,6 +24348,9 @@
       <c r="G520" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J520" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N520" s="4"/>
     </row>
     <row r="521" spans="1:14" x14ac:dyDescent="0.2">
@@ -24210,6 +24375,9 @@
       <c r="G521" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J521" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N521" s="4"/>
     </row>
     <row r="522" spans="1:14" x14ac:dyDescent="0.2">
@@ -24234,6 +24402,9 @@
       <c r="G522" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J522" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N522" s="4"/>
     </row>
     <row r="523" spans="1:14" x14ac:dyDescent="0.2">
@@ -24258,6 +24429,9 @@
       <c r="G523" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J523" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N523" s="4"/>
     </row>
     <row r="524" spans="1:14" x14ac:dyDescent="0.2">
@@ -24282,6 +24456,9 @@
       <c r="G524" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J524" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N524" s="4"/>
     </row>
     <row r="525" spans="1:14" x14ac:dyDescent="0.2">
@@ -24306,6 +24483,9 @@
       <c r="G525" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J525" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N525" s="4"/>
     </row>
     <row r="526" spans="1:14" x14ac:dyDescent="0.2">
@@ -24330,6 +24510,9 @@
       <c r="G526" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J526" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N526" s="4"/>
     </row>
     <row r="527" spans="1:14" x14ac:dyDescent="0.2">
@@ -24354,6 +24537,9 @@
       <c r="G527" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J527" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N527" s="4"/>
     </row>
     <row r="528" spans="1:14" x14ac:dyDescent="0.2">
@@ -24378,6 +24564,9 @@
       <c r="G528" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J528" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N528" s="4"/>
     </row>
     <row r="529" spans="1:14" x14ac:dyDescent="0.2">
@@ -24402,6 +24591,9 @@
       <c r="G529" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J529" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N529" s="4"/>
     </row>
     <row r="530" spans="1:14" x14ac:dyDescent="0.2">
@@ -24426,6 +24618,9 @@
       <c r="G530" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J530" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N530" s="4"/>
     </row>
     <row r="531" spans="1:14" x14ac:dyDescent="0.2">
@@ -24450,6 +24645,9 @@
       <c r="G531" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J531" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N531" s="4"/>
     </row>
     <row r="532" spans="1:14" x14ac:dyDescent="0.2">
@@ -24474,6 +24672,9 @@
       <c r="G532" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J532" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N532" s="4"/>
     </row>
     <row r="533" spans="1:14" x14ac:dyDescent="0.2">
@@ -24498,6 +24699,9 @@
       <c r="G533" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J533" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N533" s="4"/>
     </row>
     <row r="534" spans="1:14" x14ac:dyDescent="0.2">
@@ -24522,6 +24726,9 @@
       <c r="G534" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J534" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N534" s="4"/>
     </row>
     <row r="535" spans="1:14" x14ac:dyDescent="0.2">
@@ -24546,6 +24753,9 @@
       <c r="G535" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J535" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N535" s="4" t="s">
         <v>695</v>
       </c>
@@ -24572,6 +24782,9 @@
       <c r="G536" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J536" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N536" s="4"/>
     </row>
     <row r="537" spans="1:14" x14ac:dyDescent="0.2">
@@ -24596,6 +24809,9 @@
       <c r="G537" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J537" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N537" s="4"/>
     </row>
     <row r="538" spans="1:14" x14ac:dyDescent="0.2">
@@ -24620,6 +24836,9 @@
       <c r="G538" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J538" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N538" s="4" t="s">
         <v>695</v>
       </c>
@@ -24646,6 +24865,9 @@
       <c r="G539" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J539" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N539" s="4"/>
     </row>
     <row r="540" spans="1:14" x14ac:dyDescent="0.2">
@@ -24670,6 +24892,9 @@
       <c r="G540" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J540" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N540" s="4"/>
     </row>
     <row r="541" spans="1:14" x14ac:dyDescent="0.2">
@@ -24694,6 +24919,9 @@
       <c r="G541" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J541" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N541" s="4"/>
     </row>
     <row r="542" spans="1:14" x14ac:dyDescent="0.2">
@@ -24718,6 +24946,9 @@
       <c r="G542" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J542" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N542" s="4"/>
     </row>
     <row r="543" spans="1:14" x14ac:dyDescent="0.2">
@@ -24742,6 +24973,9 @@
       <c r="G543" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J543" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N543" s="4"/>
     </row>
     <row r="544" spans="1:14" x14ac:dyDescent="0.2">
@@ -24766,6 +25000,9 @@
       <c r="G544" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J544" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N544" s="4" t="s">
         <v>695</v>
       </c>
@@ -24792,6 +25029,9 @@
       <c r="G545" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J545" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N545" s="4"/>
     </row>
     <row r="546" spans="1:14" x14ac:dyDescent="0.2">
@@ -24816,6 +25056,9 @@
       <c r="G546" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J546" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N546" s="4" t="s">
         <v>695</v>
       </c>
@@ -24842,6 +25085,9 @@
       <c r="G547" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J547" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N547" s="4" t="s">
         <v>695</v>
       </c>
@@ -24868,6 +25114,9 @@
       <c r="G548" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J548" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="N548" s="4" t="s">
         <v>695</v>
       </c>
@@ -24894,6 +25143,9 @@
       <c r="G549" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J549" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="550" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A550" s="3">
@@ -24917,6 +25169,9 @@
       <c r="G550" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J550" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="551" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A551" s="3">
@@ -24940,6 +25195,48 @@
       <c r="G551" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="J551" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="552" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J552" s="5"/>
+    </row>
+    <row r="553" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J553" s="5"/>
+    </row>
+    <row r="554" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J554" s="5"/>
+    </row>
+    <row r="555" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J555" s="5"/>
+    </row>
+    <row r="556" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J556" s="5"/>
+    </row>
+    <row r="557" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J557" s="5"/>
+    </row>
+    <row r="558" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J558" s="5"/>
+    </row>
+    <row r="559" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J559" s="5"/>
+    </row>
+    <row r="560" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J560" s="5"/>
+    </row>
+    <row r="561" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J561" s="5"/>
+    </row>
+    <row r="562" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J562" s="5"/>
+    </row>
+    <row r="563" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J563" s="5"/>
+    </row>
+    <row r="564" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J564" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Herpeton Anole Data.xlsx
+++ b/Herpeton Anole Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasminekesselring/Desktop/Anole_Biometry_Practice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705886DC-3460-7649-8F9D-057971E7131D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EF96BF-EFF3-684B-B2C6-83B1AF96BACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="500" yWindow="660" windowWidth="18660" windowHeight="17160" xr2:uid="{5183197B-93B4-694E-BC06-28ADA81A1872}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{5183197B-93B4-694E-BC06-28ADA81A1872}"/>
   </bookViews>
   <sheets>
     <sheet name="Anole Master Sheet" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4391" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4391" uniqueCount="734">
   <si>
     <t>Collection_Date</t>
   </si>
@@ -1326,9 +1326,6 @@
   </si>
   <si>
     <t>USF013</t>
-  </si>
-  <si>
-    <t>N?</t>
   </si>
   <si>
     <t>Adult Raillietiellid in oral cavity (Collected; ID pending)</t>
@@ -2983,7 +2980,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>7</v>
@@ -15622,19 +15619,19 @@
         <v>17</v>
       </c>
       <c r="J294" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="K294" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="L294" s="34">
+        <v>0</v>
+      </c>
+      <c r="M294" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N294" s="37" t="s">
         <v>417</v>
-      </c>
-      <c r="K294" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="L294" s="34">
-        <v>0</v>
-      </c>
-      <c r="M294" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="N294" s="37" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.2">
@@ -15642,7 +15639,7 @@
         <v>46079</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C295" s="4" t="s">
         <v>24</v>
@@ -15684,7 +15681,7 @@
         <v>46079</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C296" s="4" t="s">
         <v>24</v>
@@ -15726,7 +15723,7 @@
         <v>46079</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C297" s="4" t="s">
         <v>14</v>
@@ -15768,7 +15765,7 @@
         <v>46079</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C298" s="4" t="s">
         <v>14</v>
@@ -15810,7 +15807,7 @@
         <v>46079</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C299" s="4" t="s">
         <v>24</v>
@@ -15852,7 +15849,7 @@
         <v>46079</v>
       </c>
       <c r="B300" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C300" s="9" t="s">
         <v>14</v>
@@ -15888,7 +15885,7 @@
         <v>19</v>
       </c>
       <c r="N300" s="28" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.2">
@@ -15896,7 +15893,7 @@
         <v>46079</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>14</v>
@@ -15938,7 +15935,7 @@
         <v>46091</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>14</v>
@@ -15974,7 +15971,7 @@
         <v>19</v>
       </c>
       <c r="N302" s="38" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.2">
@@ -15982,7 +15979,7 @@
         <v>46091</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>24</v>
@@ -16024,7 +16021,7 @@
         <v>46091</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>14</v>
@@ -16066,7 +16063,7 @@
         <v>46091</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>24</v>
@@ -16108,7 +16105,7 @@
         <v>46091</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>14</v>
@@ -16144,7 +16141,7 @@
         <v>19</v>
       </c>
       <c r="N306" s="31" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.2">
@@ -16152,7 +16149,7 @@
         <v>46091</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C307" s="4" t="s">
         <v>24</v>
@@ -16188,7 +16185,7 @@
         <v>18</v>
       </c>
       <c r="N307" s="30" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.2">
@@ -16196,7 +16193,7 @@
         <v>46091</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>24</v>
@@ -16238,7 +16235,7 @@
         <v>46091</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>14</v>
@@ -16280,7 +16277,7 @@
         <v>46091</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C310" s="4" t="s">
         <v>14</v>
@@ -16322,7 +16319,7 @@
         <v>46091</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>24</v>
@@ -16364,7 +16361,7 @@
         <v>46091</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C312" s="4" t="s">
         <v>14</v>
@@ -16406,7 +16403,7 @@
         <v>46091</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C313" s="4" t="s">
         <v>24</v>
@@ -16448,7 +16445,7 @@
         <v>46091</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C314" s="4" t="s">
         <v>24</v>
@@ -16490,7 +16487,7 @@
         <v>46091</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C315" s="4" t="s">
         <v>24</v>
@@ -16532,7 +16529,7 @@
         <v>46091</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C316" s="4" t="s">
         <v>14</v>
@@ -16574,7 +16571,7 @@
         <v>46091</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C317" s="4" t="s">
         <v>14</v>
@@ -16616,7 +16613,7 @@
         <v>46102</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C318" s="4" t="s">
         <v>14</v>
@@ -16652,7 +16649,7 @@
         <v>19</v>
       </c>
       <c r="N318" s="38" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.2">
@@ -16660,7 +16657,7 @@
         <v>46102</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C319" s="4" t="s">
         <v>14</v>
@@ -16684,19 +16681,19 @@
         <v>17</v>
       </c>
       <c r="J319" s="5" t="s">
-        <v>417</v>
+        <v>18</v>
       </c>
       <c r="K319" s="5" t="s">
         <v>17</v>
       </c>
       <c r="L319" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="M319" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="M319" s="5" t="s">
+      <c r="N319" s="30" t="s">
         <v>450</v>
-      </c>
-      <c r="N319" s="30" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.2">
@@ -16704,7 +16701,7 @@
         <v>46102</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C320" s="4" t="s">
         <v>24</v>
@@ -16746,7 +16743,7 @@
         <v>46102</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C321" s="4" t="s">
         <v>14</v>
@@ -16788,7 +16785,7 @@
         <v>46102</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C322" s="4" t="s">
         <v>14</v>
@@ -16830,7 +16827,7 @@
         <v>46102</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C323" s="4" t="s">
         <v>14</v>
@@ -16872,7 +16869,7 @@
         <v>46102</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C324" s="4" t="s">
         <v>24</v>
@@ -16914,7 +16911,7 @@
         <v>46102</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C325" s="4" t="s">
         <v>24</v>
@@ -16956,7 +16953,7 @@
         <v>46102</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C326" s="4" t="s">
         <v>24</v>
@@ -16998,7 +16995,7 @@
         <v>46102</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C327" s="4" t="s">
         <v>14</v>
@@ -17040,7 +17037,7 @@
         <v>46102</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C328" s="4" t="s">
         <v>14</v>
@@ -17076,7 +17073,7 @@
         <v>18</v>
       </c>
       <c r="N328" s="31" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.2">
@@ -17084,7 +17081,7 @@
         <v>46102</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C329" s="4" t="s">
         <v>14</v>
@@ -17120,7 +17117,7 @@
         <v>19</v>
       </c>
       <c r="N329" s="24" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.2">
@@ -17128,7 +17125,7 @@
         <v>46102</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C330" s="4" t="s">
         <v>14</v>
@@ -17170,7 +17167,7 @@
         <v>46102</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C331" s="4" t="s">
         <v>14</v>
@@ -17214,7 +17211,7 @@
         <v>46102</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C332" s="4" t="s">
         <v>14</v>
@@ -17256,7 +17253,7 @@
         <v>46102</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C333" s="4" t="s">
         <v>24</v>
@@ -17298,7 +17295,7 @@
         <v>46102</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C334" s="4" t="s">
         <v>24</v>
@@ -17340,7 +17337,7 @@
         <v>46102</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C335" s="4" t="s">
         <v>14</v>
@@ -17382,7 +17379,7 @@
         <v>46102</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C336" s="4" t="s">
         <v>24</v>
@@ -17424,7 +17421,7 @@
         <v>46102</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>14</v>
@@ -17466,7 +17463,7 @@
         <v>46204</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C338" s="4" t="s">
         <v>14</v>
@@ -17508,7 +17505,7 @@
         <v>46204</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C339" s="4" t="s">
         <v>14</v>
@@ -17544,7 +17541,7 @@
         <v>19</v>
       </c>
       <c r="N339" s="31" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.2">
@@ -17552,7 +17549,7 @@
         <v>46204</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C340" s="4" t="s">
         <v>14</v>
@@ -17588,7 +17585,7 @@
         <v>19</v>
       </c>
       <c r="N340" s="24" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.2">
@@ -17596,7 +17593,7 @@
         <v>46204</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C341" s="4" t="s">
         <v>14</v>
@@ -17640,7 +17637,7 @@
         <v>46204</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C342" s="4" t="s">
         <v>24</v>
@@ -17682,7 +17679,7 @@
         <v>46204</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C343" s="4" t="s">
         <v>14</v>
@@ -17718,7 +17715,7 @@
         <v>19</v>
       </c>
       <c r="N343" s="31" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.2">
@@ -17726,7 +17723,7 @@
         <v>46204</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C344" s="4" t="s">
         <v>24</v>
@@ -17768,7 +17765,7 @@
         <v>46204</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C345" s="4" t="s">
         <v>14</v>
@@ -17804,7 +17801,7 @@
         <v>19</v>
       </c>
       <c r="N345" s="24" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.2">
@@ -17812,7 +17809,7 @@
         <v>46204</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C346" s="4" t="s">
         <v>14</v>
@@ -17848,7 +17845,7 @@
         <v>19</v>
       </c>
       <c r="N346" s="24" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.2">
@@ -17856,7 +17853,7 @@
         <v>46204</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C347" s="4" t="s">
         <v>24</v>
@@ -17900,7 +17897,7 @@
         <v>46204</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C348" s="4" t="s">
         <v>24</v>
@@ -17942,7 +17939,7 @@
         <v>46204</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C349" s="4" t="s">
         <v>14</v>
@@ -17978,7 +17975,7 @@
         <v>19</v>
       </c>
       <c r="N349" s="24" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.2">
@@ -17986,7 +17983,7 @@
         <v>46204</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C350" s="4" t="s">
         <v>24</v>
@@ -18022,7 +18019,7 @@
         <v>19</v>
       </c>
       <c r="N350" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.2">
@@ -18030,7 +18027,7 @@
         <v>46204</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C351" s="4" t="s">
         <v>24</v>
@@ -18074,7 +18071,7 @@
         <v>46204</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C352" s="4" t="s">
         <v>14</v>
@@ -18116,7 +18113,7 @@
         <v>46204</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C353" s="4" t="s">
         <v>24</v>
@@ -18158,7 +18155,7 @@
         <v>46204</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C354" s="4" t="s">
         <v>24</v>
@@ -18202,7 +18199,7 @@
         <v>46204</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C355" s="4" t="s">
         <v>24</v>
@@ -18244,7 +18241,7 @@
         <v>46204</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C356" s="4" t="s">
         <v>24</v>
@@ -18280,7 +18277,7 @@
         <v>19</v>
       </c>
       <c r="N356" s="28" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.2">
@@ -18288,7 +18285,7 @@
         <v>46204</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C357" s="4" t="s">
         <v>14</v>
@@ -18324,7 +18321,7 @@
         <v>19</v>
       </c>
       <c r="N357" s="24" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.2">
@@ -18332,7 +18329,7 @@
         <v>46204</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C358" s="4" t="s">
         <v>24</v>
@@ -18368,7 +18365,7 @@
         <v>19</v>
       </c>
       <c r="N358" s="24" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.2">
@@ -18376,7 +18373,7 @@
         <v>46204</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C359" s="4" t="s">
         <v>14</v>
@@ -18412,7 +18409,7 @@
         <v>19</v>
       </c>
       <c r="N359" s="31" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.2">
@@ -18420,7 +18417,7 @@
         <v>46204</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C360" s="4" t="s">
         <v>24</v>
@@ -18462,7 +18459,7 @@
         <v>46204</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C361" s="4" t="s">
         <v>24</v>
@@ -18498,7 +18495,7 @@
         <v>19</v>
       </c>
       <c r="N361" s="24" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.2">
@@ -18506,7 +18503,7 @@
         <v>46204</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C362" s="4" t="s">
         <v>14</v>
@@ -18542,7 +18539,7 @@
         <v>19</v>
       </c>
       <c r="N362" s="24" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.2">
@@ -18550,7 +18547,7 @@
         <v>46204</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C363" s="4" t="s">
         <v>24</v>
@@ -18586,7 +18583,7 @@
         <v>19</v>
       </c>
       <c r="N363" s="24" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.2">
@@ -18594,7 +18591,7 @@
         <v>46204</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C364" s="4" t="s">
         <v>24</v>
@@ -18636,7 +18633,7 @@
         <v>46204</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C365" s="4" t="s">
         <v>14</v>
@@ -18672,7 +18669,7 @@
         <v>19</v>
       </c>
       <c r="N365" s="24" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.2">
@@ -18680,7 +18677,7 @@
         <v>46204</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C366" s="4" t="s">
         <v>14</v>
@@ -18722,7 +18719,7 @@
         <v>46204</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C367" s="4" t="s">
         <v>14</v>
@@ -18758,7 +18755,7 @@
         <v>19</v>
       </c>
       <c r="N367" s="24" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.2">
@@ -18766,7 +18763,7 @@
         <v>46204</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C368" s="4" t="s">
         <v>14</v>
@@ -18808,7 +18805,7 @@
         <v>46204</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C369" s="4" t="s">
         <v>24</v>
@@ -18844,7 +18841,7 @@
         <v>19</v>
       </c>
       <c r="N369" s="24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.2">
@@ -18852,7 +18849,7 @@
         <v>46204</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>14</v>
@@ -18888,7 +18885,7 @@
         <v>19</v>
       </c>
       <c r="N370" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.2">
@@ -18896,7 +18893,7 @@
         <v>46204</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C371" s="4" t="s">
         <v>24</v>
@@ -18938,7 +18935,7 @@
         <v>46144</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C372" s="4" t="s">
         <v>24</v>
@@ -18974,7 +18971,7 @@
         <v>19</v>
       </c>
       <c r="N372" s="39" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.2">
@@ -18982,7 +18979,7 @@
         <v>46144</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C373" s="4" t="s">
         <v>14</v>
@@ -19018,7 +19015,7 @@
         <v>19</v>
       </c>
       <c r="N373" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.2">
@@ -19026,7 +19023,7 @@
         <v>46144</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C374" s="4" t="s">
         <v>24</v>
@@ -19062,7 +19059,7 @@
         <v>19</v>
       </c>
       <c r="N374" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.2">
@@ -19070,7 +19067,7 @@
         <v>46144</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C375" s="4" t="s">
         <v>24</v>
@@ -19112,7 +19109,7 @@
         <v>46144</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C376" s="4" t="s">
         <v>14</v>
@@ -19148,7 +19145,7 @@
         <v>19</v>
       </c>
       <c r="N376" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.2">
@@ -19156,7 +19153,7 @@
         <v>46144</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C377" s="4" t="s">
         <v>24</v>
@@ -19192,7 +19189,7 @@
         <v>19</v>
       </c>
       <c r="N377" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.2">
@@ -19200,7 +19197,7 @@
         <v>46144</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C378" s="4" t="s">
         <v>24</v>
@@ -19242,7 +19239,7 @@
         <v>46177</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C379" s="4" t="s">
         <v>14</v>
@@ -19284,7 +19281,7 @@
         <v>46177</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C380" s="4" t="s">
         <v>14</v>
@@ -19326,7 +19323,7 @@
         <v>46177</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C381" s="4" t="s">
         <v>24</v>
@@ -19368,7 +19365,7 @@
         <v>46177</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C382" s="4" t="s">
         <v>24</v>
@@ -19404,7 +19401,7 @@
         <v>19</v>
       </c>
       <c r="N382" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.2">
@@ -19412,7 +19409,7 @@
         <v>46177</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C383" s="4" t="s">
         <v>14</v>
@@ -19454,7 +19451,7 @@
         <v>46177</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C384" s="4" t="s">
         <v>14</v>
@@ -19490,7 +19487,7 @@
         <v>19</v>
       </c>
       <c r="N384" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.2">
@@ -19498,7 +19495,7 @@
         <v>46177</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C385" s="4" t="s">
         <v>14</v>
@@ -19534,7 +19531,7 @@
         <v>18</v>
       </c>
       <c r="N385" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.2">
@@ -19542,7 +19539,7 @@
         <v>46177</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C386" s="4" t="s">
         <v>14</v>
@@ -19584,7 +19581,7 @@
         <v>46177</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C387" s="4" t="s">
         <v>14</v>
@@ -19620,7 +19617,7 @@
         <v>19</v>
       </c>
       <c r="N387" s="39" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.2">
@@ -19628,7 +19625,7 @@
         <v>46177</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C388" s="4" t="s">
         <v>24</v>
@@ -19670,7 +19667,7 @@
         <v>46177</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C389" s="4" t="s">
         <v>24</v>
@@ -19706,7 +19703,7 @@
         <v>18</v>
       </c>
       <c r="N389" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.2">
@@ -19714,7 +19711,7 @@
         <v>46177</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C390" s="4" t="s">
         <v>24</v>
@@ -19756,7 +19753,7 @@
         <v>46177</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C391" s="4" t="s">
         <v>14</v>
@@ -19792,7 +19789,7 @@
         <v>19</v>
       </c>
       <c r="N391" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.2">
@@ -19800,7 +19797,7 @@
         <v>46177</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C392" s="4" t="s">
         <v>24</v>
@@ -19842,7 +19839,7 @@
         <v>46177</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C393" s="4" t="s">
         <v>24</v>
@@ -19878,7 +19875,7 @@
         <v>19</v>
       </c>
       <c r="N393" s="7" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.2">
@@ -19886,7 +19883,7 @@
         <v>46177</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C394" s="4" t="s">
         <v>14</v>
@@ -19922,7 +19919,7 @@
         <v>19</v>
       </c>
       <c r="N394" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.2">
@@ -19930,7 +19927,7 @@
         <v>46177</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C395" s="4" t="s">
         <v>14</v>
@@ -19966,7 +19963,7 @@
         <v>19</v>
       </c>
       <c r="N395" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="396" spans="1:14" x14ac:dyDescent="0.2">
@@ -19974,7 +19971,7 @@
         <v>46177</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C396" s="4" t="s">
         <v>24</v>
@@ -20010,7 +20007,7 @@
         <v>19</v>
       </c>
       <c r="N396" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="397" spans="1:14" x14ac:dyDescent="0.2">
@@ -20018,7 +20015,7 @@
         <v>46177</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C397" s="4" t="s">
         <v>14</v>
@@ -20054,7 +20051,7 @@
         <v>19</v>
       </c>
       <c r="N397" s="39" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="398" spans="1:14" x14ac:dyDescent="0.2">
@@ -20062,7 +20059,7 @@
         <v>46190</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C398" s="4" t="s">
         <v>14</v>
@@ -20104,7 +20101,7 @@
         <v>46190</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C399" s="4" t="s">
         <v>24</v>
@@ -20146,7 +20143,7 @@
         <v>46190</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C400" s="4" t="s">
         <v>14</v>
@@ -20182,7 +20179,7 @@
         <v>19</v>
       </c>
       <c r="N400" s="40" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="401" spans="1:14" x14ac:dyDescent="0.2">
@@ -20190,7 +20187,7 @@
         <v>46190</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C401" s="4" t="s">
         <v>14</v>
@@ -20232,7 +20229,7 @@
         <v>46190</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C402" s="4" t="s">
         <v>14</v>
@@ -20268,7 +20265,7 @@
         <v>19</v>
       </c>
       <c r="N402" s="39" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="403" spans="1:14" x14ac:dyDescent="0.2">
@@ -20276,7 +20273,7 @@
         <v>46190</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C403" s="4" t="s">
         <v>24</v>
@@ -20312,7 +20309,7 @@
         <v>19</v>
       </c>
       <c r="N403" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="404" spans="1:14" x14ac:dyDescent="0.2">
@@ -20320,7 +20317,7 @@
         <v>46190</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C404" s="4" t="s">
         <v>14</v>
@@ -20356,7 +20353,7 @@
         <v>18</v>
       </c>
       <c r="N404" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="405" spans="1:14" x14ac:dyDescent="0.2">
@@ -20364,7 +20361,7 @@
         <v>46190</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C405" s="4" t="s">
         <v>14</v>
@@ -20406,7 +20403,7 @@
         <v>46190</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C406" s="4" t="s">
         <v>14</v>
@@ -20442,7 +20439,7 @@
         <v>18</v>
       </c>
       <c r="N406" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="407" spans="1:14" x14ac:dyDescent="0.2">
@@ -20450,7 +20447,7 @@
         <v>46190</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C407" s="4" t="s">
         <v>24</v>
@@ -20492,7 +20489,7 @@
         <v>46190</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C408" s="4" t="s">
         <v>24</v>
@@ -20534,7 +20531,7 @@
         <v>46190</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C409" s="4" t="s">
         <v>14</v>
@@ -20576,7 +20573,7 @@
         <v>46190</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C410" s="4" t="s">
         <v>24</v>
@@ -20612,7 +20609,7 @@
         <v>19</v>
       </c>
       <c r="N410" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="411" spans="1:14" x14ac:dyDescent="0.2">
@@ -20620,7 +20617,7 @@
         <v>46190</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C411" s="4" t="s">
         <v>14</v>
@@ -20656,7 +20653,7 @@
         <v>19</v>
       </c>
       <c r="N411" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="412" spans="1:14" x14ac:dyDescent="0.2">
@@ -20664,7 +20661,7 @@
         <v>46190</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C412" s="4" t="s">
         <v>24</v>
@@ -20706,7 +20703,7 @@
         <v>46190</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C413" s="4" t="s">
         <v>14</v>
@@ -20742,7 +20739,7 @@
         <v>19</v>
       </c>
       <c r="N413" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="414" spans="1:14" x14ac:dyDescent="0.2">
@@ -20750,7 +20747,7 @@
         <v>46190</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C414" s="4" t="s">
         <v>14</v>
@@ -20792,7 +20789,7 @@
         <v>46190</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C415" s="4" t="s">
         <v>14</v>
@@ -20834,7 +20831,7 @@
         <v>46190</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C416" s="4" t="s">
         <v>24</v>
@@ -20870,7 +20867,7 @@
         <v>19</v>
       </c>
       <c r="N416" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="417" spans="1:14" x14ac:dyDescent="0.2">
@@ -20878,7 +20875,7 @@
         <v>46190</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C417" s="4" t="s">
         <v>24</v>
@@ -20920,7 +20917,7 @@
         <v>46190</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C418" s="4" t="s">
         <v>14</v>
@@ -20962,7 +20959,7 @@
         <v>46190</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C419" s="4" t="s">
         <v>14</v>
@@ -20998,7 +20995,7 @@
         <v>19</v>
       </c>
       <c r="N419" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="420" spans="1:14" x14ac:dyDescent="0.2">
@@ -21006,7 +21003,7 @@
         <v>46190</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C420" s="4" t="s">
         <v>14</v>
@@ -21048,7 +21045,7 @@
         <v>46190</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C421" s="4" t="s">
         <v>14</v>
@@ -21090,7 +21087,7 @@
         <v>46190</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C422" s="4" t="s">
         <v>24</v>
@@ -21132,7 +21129,7 @@
         <v>46190</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C423" s="4" t="s">
         <v>24</v>
@@ -21174,7 +21171,7 @@
         <v>46190</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C424" s="4" t="s">
         <v>14</v>
@@ -21216,7 +21213,7 @@
         <v>46190</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C425" s="4" t="s">
         <v>14</v>
@@ -21258,7 +21255,7 @@
         <v>46190</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C426" s="4" t="s">
         <v>24</v>
@@ -21294,7 +21291,7 @@
         <v>19</v>
       </c>
       <c r="N426" s="7" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="427" spans="1:14" x14ac:dyDescent="0.2">
@@ -21302,7 +21299,7 @@
         <v>46190</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C427" s="4" t="s">
         <v>14</v>
@@ -21344,7 +21341,7 @@
         <v>46190</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C428" s="4" t="s">
         <v>14</v>
@@ -21386,7 +21383,7 @@
         <v>46190</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C429" s="4" t="s">
         <v>24</v>
@@ -21428,7 +21425,7 @@
         <v>46190</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C430" s="4" t="s">
         <v>24</v>
@@ -21464,7 +21461,7 @@
         <v>19</v>
       </c>
       <c r="N430" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="431" spans="1:14" x14ac:dyDescent="0.2">
@@ -21472,7 +21469,7 @@
         <v>46190</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C431" s="4" t="s">
         <v>24</v>
@@ -21514,7 +21511,7 @@
         <v>46190</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C432" s="4" t="s">
         <v>24</v>
@@ -21550,7 +21547,7 @@
         <v>19</v>
       </c>
       <c r="N432" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="433" spans="1:14" x14ac:dyDescent="0.2">
@@ -21558,7 +21555,7 @@
         <v>46190</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C433" s="4" t="s">
         <v>24</v>
@@ -21600,7 +21597,7 @@
         <v>46190</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C434" s="4" t="s">
         <v>14</v>
@@ -21642,7 +21639,7 @@
         <v>46190</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C435" s="4" t="s">
         <v>24</v>
@@ -21684,7 +21681,7 @@
         <v>46190</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C436" s="4" t="s">
         <v>14</v>
@@ -21726,7 +21723,7 @@
         <v>46190</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C437" s="4" t="s">
         <v>14</v>
@@ -21768,7 +21765,7 @@
         <v>46190</v>
       </c>
       <c r="B438" s="9" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C438" s="9" t="s">
         <v>14</v>
@@ -21804,7 +21801,7 @@
         <v>19</v>
       </c>
       <c r="N438" s="9" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="439" spans="1:14" x14ac:dyDescent="0.2">
@@ -21812,7 +21809,7 @@
         <v>46190</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C439" s="4" t="s">
         <v>14</v>
@@ -21854,7 +21851,7 @@
         <v>46190</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C440" s="4" t="s">
         <v>14</v>
@@ -21890,7 +21887,7 @@
         <v>18</v>
       </c>
       <c r="N440" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="441" spans="1:14" x14ac:dyDescent="0.2">
@@ -21898,7 +21895,7 @@
         <v>46190</v>
       </c>
       <c r="B441" s="9" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C441" s="9" t="s">
         <v>14</v>
@@ -21934,7 +21931,7 @@
         <v>19</v>
       </c>
       <c r="N441" s="9" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="442" spans="1:14" x14ac:dyDescent="0.2">
@@ -21942,7 +21939,7 @@
         <v>46190</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C442" s="4" t="s">
         <v>14</v>
@@ -21978,7 +21975,7 @@
         <v>19</v>
       </c>
       <c r="N442" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="443" spans="1:14" x14ac:dyDescent="0.2">
@@ -21986,7 +21983,7 @@
         <v>46190</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C443" s="4" t="s">
         <v>24</v>
@@ -22028,7 +22025,7 @@
         <v>46190</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C444" s="4" t="s">
         <v>14</v>
@@ -22064,7 +22061,7 @@
         <v>18</v>
       </c>
       <c r="N444" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="445" spans="1:14" x14ac:dyDescent="0.2">
@@ -22072,7 +22069,7 @@
         <v>46190</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C445" s="4" t="s">
         <v>14</v>
@@ -22108,7 +22105,7 @@
         <v>19</v>
       </c>
       <c r="N445" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="446" spans="1:14" x14ac:dyDescent="0.2">
@@ -22116,7 +22113,7 @@
         <v>46190</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C446" s="4" t="s">
         <v>24</v>
@@ -22158,7 +22155,7 @@
         <v>46190</v>
       </c>
       <c r="B447" s="9" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C447" s="9" t="s">
         <v>14</v>
@@ -22194,7 +22191,7 @@
         <v>18</v>
       </c>
       <c r="N447" s="9" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="448" spans="1:14" x14ac:dyDescent="0.2">
@@ -22202,7 +22199,7 @@
         <v>46190</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C448" s="4" t="s">
         <v>24</v>
@@ -22244,7 +22241,7 @@
         <v>46190</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C449" s="4" t="s">
         <v>24</v>
@@ -22286,7 +22283,7 @@
         <v>46190</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C450" s="4" t="s">
         <v>24</v>
@@ -22328,7 +22325,7 @@
         <v>46190</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C451" s="4" t="s">
         <v>24</v>
@@ -22370,7 +22367,7 @@
         <v>46190</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C452" s="4" t="s">
         <v>24</v>
@@ -22414,7 +22411,7 @@
         <v>46190</v>
       </c>
       <c r="B453" s="9" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C453" s="9" t="s">
         <v>14</v>
@@ -22450,7 +22447,7 @@
         <v>18</v>
       </c>
       <c r="N453" s="9" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="454" spans="1:14" x14ac:dyDescent="0.2">
@@ -22458,7 +22455,7 @@
         <v>46190</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C454" s="4" t="s">
         <v>24</v>
@@ -22500,7 +22497,7 @@
         <v>46190</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C455" s="4" t="s">
         <v>24</v>
@@ -22542,7 +22539,7 @@
         <v>46190</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C456" s="4" t="s">
         <v>14</v>
@@ -22578,7 +22575,7 @@
         <v>19</v>
       </c>
       <c r="N456" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="457" spans="1:14" x14ac:dyDescent="0.2">
@@ -22586,7 +22583,7 @@
         <v>46190</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C457" s="4" t="s">
         <v>24</v>
@@ -22628,7 +22625,7 @@
         <v>46190</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C458" s="4" t="s">
         <v>24</v>
@@ -22664,7 +22661,7 @@
         <v>19</v>
       </c>
       <c r="N458" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="459" spans="1:14" x14ac:dyDescent="0.2">
@@ -22672,7 +22669,7 @@
         <v>46190</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C459" s="4" t="s">
         <v>14</v>
@@ -22714,7 +22711,7 @@
         <v>46190</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C460" s="4" t="s">
         <v>24</v>
@@ -22756,7 +22753,7 @@
         <v>46190</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C461" s="4" t="s">
         <v>24</v>
@@ -22798,7 +22795,7 @@
         <v>46100</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C462" s="4" t="s">
         <v>14</v>
@@ -22826,7 +22823,7 @@
         <v>46100</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C463" s="4" t="s">
         <v>14</v>
@@ -22854,7 +22851,7 @@
         <v>46100</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C464" s="4" t="s">
         <v>14</v>
@@ -22882,10 +22879,10 @@
         <v>46100</v>
       </c>
       <c r="B465" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="C465" s="4" t="s">
         <v>646</v>
-      </c>
-      <c r="C465" s="4" t="s">
-        <v>647</v>
       </c>
       <c r="D465" s="4">
         <v>4.8</v>
@@ -22910,7 +22907,7 @@
         <v>46100</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C466" s="4" t="s">
         <v>24</v>
@@ -22938,7 +22935,7 @@
         <v>46100</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C467" s="4" t="s">
         <v>14</v>
@@ -22964,7 +22961,7 @@
         <v>46100</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C468" s="4" t="s">
         <v>14</v>
@@ -22990,7 +22987,7 @@
         <v>46100</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C469" s="4" t="s">
         <v>14</v>
@@ -23016,10 +23013,10 @@
         <v>46100</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D470" s="4">
         <v>4.5</v>
@@ -23042,7 +23039,7 @@
         <v>46100</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C471" s="4" t="s">
         <v>14</v>
@@ -23068,7 +23065,7 @@
         <v>46100</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C472" s="4" t="s">
         <v>14</v>
@@ -23094,7 +23091,7 @@
         <v>46100</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C473" s="4" t="s">
         <v>24</v>
@@ -23120,7 +23117,7 @@
         <v>46100</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C474" s="4" t="s">
         <v>14</v>
@@ -23146,7 +23143,7 @@
         <v>46100</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C475" s="4" t="s">
         <v>24</v>
@@ -23172,7 +23169,7 @@
         <v>46100</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C476" s="4" t="s">
         <v>24</v>
@@ -23198,7 +23195,7 @@
         <v>46100</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C477" s="4" t="s">
         <v>14</v>
@@ -23224,7 +23221,7 @@
         <v>46100</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C478" s="4" t="s">
         <v>14</v>
@@ -23250,7 +23247,7 @@
         <v>46100</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C479" s="4" t="s">
         <v>14</v>
@@ -23276,7 +23273,7 @@
         <v>46100</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C480" s="4" t="s">
         <v>24</v>
@@ -23302,7 +23299,7 @@
         <v>46100</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C481" s="4" t="s">
         <v>24</v>
@@ -23328,7 +23325,7 @@
         <v>46100</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C482" s="4" t="s">
         <v>14</v>
@@ -23354,7 +23351,7 @@
         <v>46100</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C483" s="4" t="s">
         <v>14</v>
@@ -23380,7 +23377,7 @@
         <v>46100</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C484" s="4" t="s">
         <v>14</v>
@@ -23406,7 +23403,7 @@
         <v>46100</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C485" s="4" t="s">
         <v>14</v>
@@ -23432,7 +23429,7 @@
         <v>46100</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C486" s="4" t="s">
         <v>14</v>
@@ -23458,7 +23455,7 @@
         <v>46100</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C487" s="4" t="s">
         <v>24</v>
@@ -23484,7 +23481,7 @@
         <v>46100</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C488" s="4" t="s">
         <v>14</v>
@@ -23510,7 +23507,7 @@
         <v>46100</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C489" s="4" t="s">
         <v>24</v>
@@ -23536,7 +23533,7 @@
         <v>46100</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C490" s="4" t="s">
         <v>24</v>
@@ -23562,7 +23559,7 @@
         <v>46100</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C491" s="4" t="s">
         <v>14</v>
@@ -23588,7 +23585,7 @@
         <v>46100</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C492" s="4" t="s">
         <v>24</v>
@@ -23614,7 +23611,7 @@
         <v>46100</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C493" s="4" t="s">
         <v>14</v>
@@ -23640,7 +23637,7 @@
         <v>46100</v>
       </c>
       <c r="B494" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C494" s="4" t="s">
         <v>14</v>
@@ -23666,7 +23663,7 @@
         <v>46100</v>
       </c>
       <c r="B495" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C495" s="4" t="s">
         <v>14</v>
@@ -23692,7 +23689,7 @@
         <v>46100</v>
       </c>
       <c r="B496" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C496" s="4" t="s">
         <v>24</v>
@@ -23718,7 +23715,7 @@
         <v>46100</v>
       </c>
       <c r="B497" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C497" s="4" t="s">
         <v>24</v>
@@ -23744,7 +23741,7 @@
         <v>46100</v>
       </c>
       <c r="B498" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C498" s="4" t="s">
         <v>24</v>
@@ -23770,7 +23767,7 @@
         <v>46100</v>
       </c>
       <c r="B499" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C499" s="4" t="s">
         <v>14</v>
@@ -23796,7 +23793,7 @@
         <v>46100</v>
       </c>
       <c r="B500" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C500" s="4" t="s">
         <v>24</v>
@@ -23822,7 +23819,7 @@
         <v>46100</v>
       </c>
       <c r="B501" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C501" s="4" t="s">
         <v>14</v>
@@ -23848,7 +23845,7 @@
         <v>46100</v>
       </c>
       <c r="B502" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C502" s="4" t="s">
         <v>14</v>
@@ -23874,7 +23871,7 @@
         <v>46100</v>
       </c>
       <c r="B503" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C503" s="4" t="s">
         <v>24</v>
@@ -23900,7 +23897,7 @@
         <v>46100</v>
       </c>
       <c r="B504" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C504" s="4" t="s">
         <v>14</v>
@@ -23926,7 +23923,7 @@
         <v>46100</v>
       </c>
       <c r="B505" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C505" s="4" t="s">
         <v>24</v>
@@ -23952,7 +23949,7 @@
         <v>46100</v>
       </c>
       <c r="B506" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C506" s="4" t="s">
         <v>24</v>
@@ -23978,7 +23975,7 @@
         <v>46100</v>
       </c>
       <c r="B507" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C507" s="4" t="s">
         <v>24</v>
@@ -24004,7 +24001,7 @@
         <v>46225</v>
       </c>
       <c r="B508" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C508" s="4" t="s">
         <v>14</v>
@@ -24030,7 +24027,7 @@
         <v>46225</v>
       </c>
       <c r="B509" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C509" s="4" t="s">
         <v>14</v>
@@ -24056,7 +24053,7 @@
         <v>46225</v>
       </c>
       <c r="B510" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C510" s="4" t="s">
         <v>14</v>
@@ -24082,7 +24079,7 @@
         <v>46225</v>
       </c>
       <c r="B511" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C511" s="4" t="s">
         <v>14</v>
@@ -24109,7 +24106,7 @@
         <v>46225</v>
       </c>
       <c r="B512" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C512" s="4" t="s">
         <v>24</v>
@@ -24130,7 +24127,7 @@
         <v>18</v>
       </c>
       <c r="N512" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="513" spans="1:14" x14ac:dyDescent="0.2">
@@ -24138,7 +24135,7 @@
         <v>46225</v>
       </c>
       <c r="B513" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C513" s="41" t="s">
         <v>14</v>
@@ -24165,7 +24162,7 @@
         <v>46225</v>
       </c>
       <c r="B514" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C514" s="41" t="s">
         <v>14</v>
@@ -24192,7 +24189,7 @@
         <v>46225</v>
       </c>
       <c r="B515" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C515" s="4" t="s">
         <v>24</v>
@@ -24213,7 +24210,7 @@
         <v>18</v>
       </c>
       <c r="N515" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="516" spans="1:14" x14ac:dyDescent="0.2">
@@ -24221,7 +24218,7 @@
         <v>46225</v>
       </c>
       <c r="B516" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C516" s="4" t="s">
         <v>24</v>
@@ -24242,7 +24239,7 @@
         <v>18</v>
       </c>
       <c r="N516" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="517" spans="1:14" x14ac:dyDescent="0.2">
@@ -24250,7 +24247,7 @@
         <v>46225</v>
       </c>
       <c r="B517" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C517" s="4" t="s">
         <v>14</v>
@@ -24277,7 +24274,7 @@
         <v>46225</v>
       </c>
       <c r="B518" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C518" s="4" t="s">
         <v>14</v>
@@ -24304,7 +24301,7 @@
         <v>46225</v>
       </c>
       <c r="B519" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C519" s="4" t="s">
         <v>14</v>
@@ -24331,7 +24328,7 @@
         <v>46225</v>
       </c>
       <c r="B520" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C520" s="4" t="s">
         <v>14</v>
@@ -24358,7 +24355,7 @@
         <v>46225</v>
       </c>
       <c r="B521" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C521" s="4" t="s">
         <v>14</v>
@@ -24385,7 +24382,7 @@
         <v>46225</v>
       </c>
       <c r="B522" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C522" s="4" t="s">
         <v>14</v>
@@ -24412,7 +24409,7 @@
         <v>46225</v>
       </c>
       <c r="B523" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C523" s="4" t="s">
         <v>14</v>
@@ -24439,7 +24436,7 @@
         <v>46225</v>
       </c>
       <c r="B524" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C524" s="4" t="s">
         <v>14</v>
@@ -24466,7 +24463,7 @@
         <v>46225</v>
       </c>
       <c r="B525" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C525" s="4" t="s">
         <v>14</v>
@@ -24493,7 +24490,7 @@
         <v>46225</v>
       </c>
       <c r="B526" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C526" s="4" t="s">
         <v>14</v>
@@ -24520,7 +24517,7 @@
         <v>46225</v>
       </c>
       <c r="B527" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C527" s="4" t="s">
         <v>14</v>
@@ -24547,7 +24544,7 @@
         <v>46225</v>
       </c>
       <c r="B528" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C528" s="4" t="s">
         <v>24</v>
@@ -24574,7 +24571,7 @@
         <v>46225</v>
       </c>
       <c r="B529" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C529" s="4" t="s">
         <v>14</v>
@@ -24601,7 +24598,7 @@
         <v>46225</v>
       </c>
       <c r="B530" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C530" s="4" t="s">
         <v>24</v>
@@ -24628,7 +24625,7 @@
         <v>46225</v>
       </c>
       <c r="B531" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C531" s="4" t="s">
         <v>24</v>
@@ -24655,7 +24652,7 @@
         <v>46225</v>
       </c>
       <c r="B532" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C532" s="4" t="s">
         <v>14</v>
@@ -24682,7 +24679,7 @@
         <v>46225</v>
       </c>
       <c r="B533" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C533" s="4" t="s">
         <v>24</v>
@@ -24709,7 +24706,7 @@
         <v>46225</v>
       </c>
       <c r="B534" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C534" s="4" t="s">
         <v>24</v>
@@ -24736,7 +24733,7 @@
         <v>46225</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C535" s="4" t="s">
         <v>24</v>
@@ -24757,7 +24754,7 @@
         <v>18</v>
       </c>
       <c r="N535" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="536" spans="1:14" x14ac:dyDescent="0.2">
@@ -24765,7 +24762,7 @@
         <v>46225</v>
       </c>
       <c r="B536" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C536" s="4" t="s">
         <v>24</v>
@@ -24792,7 +24789,7 @@
         <v>46225</v>
       </c>
       <c r="B537" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C537" s="4" t="s">
         <v>24</v>
@@ -24819,7 +24816,7 @@
         <v>46225</v>
       </c>
       <c r="B538" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C538" s="4" t="s">
         <v>24</v>
@@ -24840,7 +24837,7 @@
         <v>18</v>
       </c>
       <c r="N538" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="539" spans="1:14" x14ac:dyDescent="0.2">
@@ -24848,7 +24845,7 @@
         <v>46225</v>
       </c>
       <c r="B539" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C539" s="4" t="s">
         <v>24</v>
@@ -24875,7 +24872,7 @@
         <v>46225</v>
       </c>
       <c r="B540" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C540" s="4" t="s">
         <v>24</v>
@@ -24902,7 +24899,7 @@
         <v>46225</v>
       </c>
       <c r="B541" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C541" s="4" t="s">
         <v>14</v>
@@ -24929,7 +24926,7 @@
         <v>46225</v>
       </c>
       <c r="B542" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C542" s="4" t="s">
         <v>24</v>
@@ -24956,7 +24953,7 @@
         <v>46225</v>
       </c>
       <c r="B543" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C543" s="4" t="s">
         <v>24</v>
@@ -24983,7 +24980,7 @@
         <v>46225</v>
       </c>
       <c r="B544" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C544" s="4" t="s">
         <v>24</v>
@@ -25004,7 +25001,7 @@
         <v>18</v>
       </c>
       <c r="N544" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="545" spans="1:14" x14ac:dyDescent="0.2">
@@ -25012,7 +25009,7 @@
         <v>46225</v>
       </c>
       <c r="B545" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C545" s="4" t="s">
         <v>24</v>
@@ -25039,10 +25036,10 @@
         <v>46225</v>
       </c>
       <c r="B546" s="4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D546" s="4">
         <v>4.4000000000000004</v>
@@ -25060,7 +25057,7 @@
         <v>18</v>
       </c>
       <c r="N546" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="547" spans="1:14" x14ac:dyDescent="0.2">
@@ -25068,7 +25065,7 @@
         <v>46225</v>
       </c>
       <c r="B547" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C547" s="41" t="s">
         <v>24</v>
@@ -25089,7 +25086,7 @@
         <v>18</v>
       </c>
       <c r="N547" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="548" spans="1:14" x14ac:dyDescent="0.2">
@@ -25097,7 +25094,7 @@
         <v>46225</v>
       </c>
       <c r="B548" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C548" s="41" t="s">
         <v>24</v>
@@ -25118,7 +25115,7 @@
         <v>18</v>
       </c>
       <c r="N548" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="549" spans="1:14" x14ac:dyDescent="0.2">
@@ -25126,7 +25123,7 @@
         <v>46225</v>
       </c>
       <c r="B549" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C549" s="4" t="s">
         <v>14</v>
@@ -25152,7 +25149,7 @@
         <v>46225</v>
       </c>
       <c r="B550" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C550" s="41" t="s">
         <v>24</v>
@@ -25178,7 +25175,7 @@
         <v>46225</v>
       </c>
       <c r="B551" s="4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C551" s="41" t="s">
         <v>24</v>
